--- a/UPMPackages/com.solotopia.nova.framework.sdk.iap/Nova/Tracks/Tracks.xlsx
+++ b/UPMPackages/com.solotopia.nova.framework.sdk.iap/Nova/Tracks/Tracks.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17580" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet name="打点表-IAP" sheetId="1" state="visible" r:id="rId1"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
-</workbook>
+<s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <s:workbookPr/>
+  <s:bookViews>
+    <s:workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17580" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </s:bookViews>
+  <s:sheets>
+    <s:sheet name="打点表-IAP" sheetId="1" state="visible" r:id="rId1"/>
+  </s:sheets>
+  <s:definedNames/>
+  <s:calcPr calcId="0" fullCalcOnLoad="1"/>
+</s:workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,8 +36,27 @@
       <family val="3"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体-简"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -62,8 +81,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -132,11 +157,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -170,6 +204,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -548,3893 +592,3894 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I217"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col width="35" customWidth="1" style="5" min="1" max="1"/>
-    <col width="31" customWidth="1" style="5" min="2" max="2"/>
-    <col width="55" customWidth="1" style="5" min="3" max="3"/>
+    <col width="28" customWidth="1" style="5" min="1" max="1"/>
+    <col width="18" customWidth="1" style="5" min="2" max="2"/>
+    <col width="36" customWidth="1" style="5" min="3" max="3"/>
     <col width="40" customWidth="1" style="5" min="4" max="4"/>
-    <col width="13" customWidth="1" style="5" min="5" max="5"/>
-    <col width="55" customWidth="1" style="5" min="6" max="7"/>
-    <col width="11" customWidth="1" style="5" min="8" max="8"/>
-    <col width="55" customWidth="1" style="5" min="9" max="9"/>
+    <col width="14" customWidth="1" style="5" min="5" max="5"/>
+    <col width="58" customWidth="1" style="5" min="6" max="6"/>
+    <col width="32" customWidth="1" style="5" min="7" max="7"/>
+    <col width="16" customWidth="1" style="5" min="8" max="8"/>
+    <col width="48" customWidth="1" style="5" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1" s="5">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>事件名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>事件中文名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>事件说明</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>属性名</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>属性类型</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>属性说明</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>上报时机</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>目标</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="14.5" customHeight="1" s="5">
-      <c r="A2" s="9" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>nova_iap_init</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>IAP 初始化</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>IAP Store 初始化完成或失败。</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>nova_channel</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>支付渠道名称。</t>
-        </is>
-      </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>当前 Store 稳定渠道名；未找到 Store 时来自请求 StoreType，小写；空请求使用 router。</t>
+        </is>
+      </c>
+      <c r="G2" s="16" t="inlineStr">
         <is>
           <t>Store 初始化成功或失败时上报。</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="H2" s="16" t="inlineStr">
         <is>
           <t>tga</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="16" t="inlineStr">
         <is>
           <t>失败时额外携带初始化失败原因。</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="14.5" customHeight="1" s="5">
+    <row r="3">
       <c r="A3" s="7" t="n"/>
       <c r="B3" s="7" t="n"/>
       <c r="C3" s="7" t="n"/>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>nova_iap_init_result</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>enum-string</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>IAP 初始化结果。success=初始化成功。 failed=初始化失败。</t>
         </is>
       </c>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="n"/>
-      <c r="I3" s="7" t="n"/>
-    </row>
-    <row r="4" ht="14.5" customHeight="1" s="5">
+      <c r="G3" s="16" t="n"/>
+      <c r="H3" s="16" t="n"/>
+      <c r="I3" s="16" t="n"/>
+    </row>
+    <row r="4">
       <c r="A4" s="8" t="n"/>
       <c r="B4" s="8" t="n"/>
       <c r="C4" s="8" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>nova_iap_init_failure_reason</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>IAP 初始化失败原因。</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="n"/>
-      <c r="H4" s="8" t="n"/>
-      <c r="I4" s="8" t="n"/>
-    </row>
-    <row r="5" ht="14.5" customHeight="1" s="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>仅失败时附带；使用具体 Store 的初始化失败原因整数，枚举按具体 Store 区分。 Mobile：MobileStoreInitFailureReason：0=未发生初始化失败。 ；1=平台内购服务不可用的通用兜底原因。 ；2=Unity IAP StoreController 创建失败。 ；3=Unity IAP Connect 调用抛出异常。 ；4=初始化期间商店连接断开。 ；5=初始化流程被取消。。</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="n"/>
+      <c r="H4" s="16" t="n"/>
+      <c r="I4" s="16" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>nova_iap_buy</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>发起购买</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>用户发起 IAP 购买。</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>用户发起购买；价格取支付表配置。</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>nova_table_id</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>商品配置表行 ID。</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>商品配置表行 ID；客户端使用 64 位整数。</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>用户发起真实平台购买前上报。</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t>tga</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t>调试支付也会上报该事件。</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="14.5" customHeight="1" s="5">
+    <row r="6">
       <c r="A6" s="7" t="n"/>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>nova_product_id</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>平台侧商品 ID。</t>
         </is>
       </c>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-    </row>
-    <row r="7" ht="14.5" customHeight="1" s="5">
+      <c r="G6" s="16" t="n"/>
+      <c r="H6" s="16" t="n"/>
+      <c r="I6" s="16" t="n"/>
+    </row>
+    <row r="7">
       <c r="A7" s="7" t="n"/>
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>nova_debug</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>是否测试模式。</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-    </row>
-    <row r="8" ht="14.5" customHeight="1" s="5">
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>是否 DevelopMode.Debug；不是 AlwaysPaySucceed。</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="16" t="n"/>
+      <c r="I7" s="16" t="n"/>
+    </row>
+    <row r="8">
       <c r="A8" s="7" t="n"/>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>nova_price</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>商品本地化价格数值。</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
-    </row>
-    <row r="9" ht="14.5" customHeight="1" s="5">
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>支付表 Price 配置解析的价格数值；不是平台本地化价格或可信实付金额。</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="16" t="n"/>
+      <c r="I8" s="16" t="n"/>
+    </row>
+    <row r="9">
       <c r="A9" s="7" t="n"/>
       <c r="B9" s="7" t="n"/>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>nova_channel</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>支付渠道名称。</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
-    </row>
-    <row r="10" ht="14.5" customHeight="1" s="5">
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>当前 Store 稳定渠道名；未找到 Store 时来自请求 StoreType，小写；空请求使用 router。</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="16" t="n"/>
+      <c r="I9" s="16" t="n"/>
+    </row>
+    <row r="10">
       <c r="A10" s="8" t="n"/>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>nova_custom_data</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>业务层透传的自定义字符串参数。</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-    </row>
-    <row r="11" ht="14.5" customHeight="1" s="5">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>仅业务透传字符串非空时附带；框架不解析。</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="n"/>
+      <c r="H10" s="16" t="n"/>
+      <c r="I10" s="16" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>nova_iap_local_pay_success</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>本地支付成功</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>平台侧确认支付成功但尚未完成服务端验单。</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>nova_table_id</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>商品配置表行 ID。</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>商品配置表行 ID；客户端使用 64 位整数。</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>平台返回支付成功并登记本地订单后上报。</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t>tga</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>同一平台订单在当前运行期会去重。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="14.5" customHeight="1" s="5">
+    <row r="12">
       <c r="A12" s="7" t="n"/>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>nova_product_id</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>平台侧商品 ID。</t>
         </is>
       </c>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-    </row>
-    <row r="13" ht="14.5" customHeight="1" s="5">
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="16" t="n"/>
+      <c r="I12" s="16" t="n"/>
+    </row>
+    <row r="13">
       <c r="A13" s="7" t="n"/>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>nova_debug</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>是否测试模式。</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-    </row>
-    <row r="14" ht="14.5" customHeight="1" s="5">
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>是否 DevelopMode.Debug；不是 AlwaysPaySucceed。</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="16" t="n"/>
+      <c r="I13" s="16" t="n"/>
+    </row>
+    <row r="14">
       <c r="A14" s="7" t="n"/>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>nova_price</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>商品本地化价格数值。</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="7" t="n"/>
-    </row>
-    <row r="15" ht="14.5" customHeight="1" s="5">
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>支付表 Price 配置解析的价格数值；不是平台本地化价格或可信实付金额。</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="16" t="n"/>
+      <c r="I14" s="16" t="n"/>
+    </row>
+    <row r="15">
       <c r="A15" s="7" t="n"/>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>nova_channel</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>支付渠道名称。</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-    </row>
-    <row r="16" ht="14.5" customHeight="1" s="5">
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>当前 Store 稳定渠道名；未找到 Store 时来自请求 StoreType，小写；空请求使用 router。</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="16" t="n"/>
+      <c r="I15" s="16" t="n"/>
+    </row>
+    <row r="16">
       <c r="A16" s="7" t="n"/>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>nova_order_id</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>非 ThirdPay Store 的平台或服务端订单 ID；ThirdPay 不发送此字段，使用客户端/服务端双订单号。</t>
         </is>
       </c>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-    </row>
-    <row r="17" ht="14.5" customHeight="1" s="5">
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="16" t="n"/>
+      <c r="I16" s="16" t="n"/>
+    </row>
+    <row r="17">
       <c r="A17" s="7" t="n"/>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>nova_add_order</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>是否为恢复订单或补单订单。</t>
         </is>
       </c>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
-    </row>
-    <row r="18" ht="14.5" customHeight="1" s="5">
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="16" t="n"/>
+      <c r="I17" s="16" t="n"/>
+    </row>
+    <row r="18">
       <c r="A18" s="7" t="n"/>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>nova_custom_data</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>业务层透传的自定义字符串参数。</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="7" t="n"/>
-    </row>
-    <row r="19" ht="14.5" customHeight="1" s="5">
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>仅业务透传字符串非空时附带；框架不解析。</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="n"/>
+      <c r="H18" s="16" t="n"/>
+      <c r="I18" s="16" t="n"/>
+    </row>
+    <row r="19">
       <c r="A19" s="7" t="n"/>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_open_mode</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 支付页实际打开方式：0=打开失败，1=Auth Tab，2=Custom Tabs，3=系统浏览器回退，4=嵌入式 WebView，5=iOS Safe Browsing。</t>
         </is>
       </c>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
-    </row>
-    <row r="20" ht="14.5" customHeight="1" s="5">
+      <c r="G19" s="16" t="n"/>
+      <c r="H19" s="16" t="n"/>
+      <c r="I19" s="16" t="n"/>
+    </row>
+    <row r="20">
       <c r="A20" s="7" t="n"/>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_callback_status</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>pay_callback 状态：0=未收到或无法识别，1=支付成功，2=支付失败，3=支付成功但渠道信息尚未同步。</t>
         </is>
       </c>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="7" t="n"/>
-    </row>
-    <row r="21" ht="14.5" customHeight="1" s="5">
+      <c r="G20" s="16" t="n"/>
+      <c r="H20" s="16" t="n"/>
+      <c r="I20" s="16" t="n"/>
+    </row>
+    <row r="21">
       <c r="A21" s="7" t="n"/>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_close_reason</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 关闭原因：0=未知，1=close_callback，2=嵌入式 WebView 关闭，3=iOS Safe Browsing 关闭，4=pay_callback 失败，5=未知 callback 状态，6=callback 参数无效，7=外部浏览器返回无成功 callback，8=callback 订单不匹配，9=验单开始后的迟到 callback，10=页面加载失败，11=Web 内容进程终止，12=页面异常，13=操作取消，14=会话被替换，15=Store 释放。</t>
         </is>
       </c>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="7" t="n"/>
-    </row>
-    <row r="22" ht="14.5" customHeight="1" s="5">
+      <c r="G21" s="16" t="n"/>
+      <c r="H21" s="16" t="n"/>
+      <c r="I21" s="16" t="n"/>
+    </row>
+    <row r="22">
       <c r="A22" s="7" t="n"/>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_failure_reason</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 支付/验单失败原因：0=未知，1=Store 禁用，2=Store 未初始化，3=重复支付，4=商品不存在，5=UID 缺失，6=支付配置不可用，7=服务端关闭支付，8=服务端未配置商品，9=WebView 服务不可用，10=外部浏览器服务不可用，11=Google 连接失败，12=Google token 创建失败，13=Google 支付 URL 构建失败，14=Google 用户取消，15=支付页打开失败，16=支付页打开异常，17=系统浏览器回退 URL 为空，18=callback 支付失败，19=callback 参数无效，20=callback 状态未知，21=callback 订单不匹配，22=callback 到达时已开始验单，23=外部浏览器返回无成功 callback，24=验单服务不可用，25=验单网络失败，26=验单响应缺少订单，27=服务端待支付，28=服务端处理中，29=服务端失败或过期，30=服务端订单不存在，31=未知服务端订单状态，32=操作取消，33=会话被替换，34=Store 释放，35=未分类异常，36=第三方支付 URL 构建失败，37=授权完成但支付 URL 缺失。</t>
         </is>
       </c>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="7" t="n"/>
-    </row>
-    <row r="23" ht="14.5" customHeight="1" s="5">
+      <c r="G22" s="16" t="n"/>
+      <c r="H22" s="16" t="n"/>
+      <c r="I22" s="16" t="n"/>
+    </row>
+    <row r="23">
       <c r="A23" s="7" t="n"/>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>nova_client_order_id</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>客户端生成的 ThirdPay 订单号。</t>
         </is>
       </c>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="7" t="n"/>
-    </row>
-    <row r="24" ht="14.5" customHeight="1" s="5">
+      <c r="G23" s="16" t="n"/>
+      <c r="H23" s="16" t="n"/>
+      <c r="I23" s="16" t="n"/>
+    </row>
+    <row r="24">
       <c r="A24" s="7" t="n"/>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>nova_server_order_id</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>服务端确认的 ThirdPay 订单号；无返回时为空。</t>
         </is>
       </c>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="7" t="n"/>
-    </row>
-    <row r="25" ht="14.5" customHeight="1" s="5">
+      <c r="G24" s="16" t="n"/>
+      <c r="H24" s="16" t="n"/>
+      <c r="I24" s="16" t="n"/>
+    </row>
+    <row r="25">
       <c r="A25" s="7" t="n"/>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>nova_native_error_code</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="16" t="inlineStr">
         <is>
           <t>支付页或原生能力返回的错误码；无错误时为 0。</t>
         </is>
       </c>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
-      <c r="I25" s="7" t="n"/>
-    </row>
-    <row r="26" ht="14.5" customHeight="1" s="5">
+      <c r="G25" s="16" t="n"/>
+      <c r="H25" s="16" t="n"/>
+      <c r="I25" s="16" t="n"/>
+    </row>
+    <row r="26">
       <c r="A26" s="8" t="n"/>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>nova_native_error_message</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>支付页或原生能力返回的错误描述。</t>
         </is>
       </c>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="8" t="n"/>
-    </row>
-    <row r="27" ht="24" customHeight="1" s="5">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="G26" s="16" t="n"/>
+      <c r="H26" s="16" t="n"/>
+      <c r="I26" s="16" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>nova_iap_local_pay_fail</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>本地支付失败</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>支付会话建立前的本地支付流程失败。</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>支付调用返回失败或渠道失败通知；实际边界由具体 Store 定义。</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>nova_table_id</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>商品配置表行 ID。</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>Store 前置校验、创建/授权失败或支付页未建立时上报；已有 local_pay_success/close_order 或验单失败时不重复上报。</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>商品配置表行 ID；客户端使用 64 位整数。</t>
+        </is>
+      </c>
+      <c r="G27" s="16" t="inlineStr">
+        <is>
+          <t>支付路由校验失败、Store 前置校验失败或平台购买失败通知时上报；ThirdPay 的前置失败与关闭、验单事件分开记录。</t>
+        </is>
+      </c>
+      <c r="H27" s="16" t="inlineStr">
         <is>
           <t>tga</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="16" t="inlineStr">
         <is>
           <t>失败原因由具体 Store 收敛到自己的明确枚举整数值。</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="14.5" customHeight="1" s="5">
+    <row r="28">
       <c r="A28" s="7" t="n"/>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>nova_product_id</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>平台侧商品 ID。</t>
         </is>
       </c>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="7" t="n"/>
-    </row>
-    <row r="29" ht="14.5" customHeight="1" s="5">
+      <c r="G28" s="16" t="n"/>
+      <c r="H28" s="16" t="n"/>
+      <c r="I28" s="16" t="n"/>
+    </row>
+    <row r="29">
       <c r="A29" s="7" t="n"/>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>nova_debug</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>是否测试模式。</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="7" t="n"/>
-      <c r="I29" s="7" t="n"/>
-    </row>
-    <row r="30" ht="14.5" customHeight="1" s="5">
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>是否 DevelopMode.Debug；不是 AlwaysPaySucceed。</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="n"/>
+      <c r="H29" s="16" t="n"/>
+      <c r="I29" s="16" t="n"/>
+    </row>
+    <row r="30">
       <c r="A30" s="7" t="n"/>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>nova_price</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>商品本地化价格数值。</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="7" t="n"/>
-    </row>
-    <row r="31" ht="14.5" customHeight="1" s="5">
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>支付表 Price 配置解析的价格数值；不是平台本地化价格或可信实付金额。</t>
+        </is>
+      </c>
+      <c r="G30" s="16" t="n"/>
+      <c r="H30" s="16" t="n"/>
+      <c r="I30" s="16" t="n"/>
+    </row>
+    <row r="31">
       <c r="A31" s="7" t="n"/>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>nova_channel</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>支付渠道名称。</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="7" t="n"/>
-    </row>
-    <row r="32" ht="14.5" customHeight="1" s="5">
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>当前 Store 稳定渠道名；未找到 Store 时来自请求 StoreType，小写；空请求使用 router。</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="n"/>
+      <c r="H31" s="16" t="n"/>
+      <c r="I31" s="16" t="n"/>
+    </row>
+    <row r="32">
       <c r="A32" s="7" t="n"/>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>nova_reason</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>失败原因枚举整数值。</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="n"/>
-      <c r="I32" s="7" t="n"/>
-    </row>
-    <row r="33" ht="14.5" customHeight="1" s="5">
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>IAPPluginErrorCode：0=无错误（保留，未使用）。 ；1=目标 store 不可用、未找到或已被禁用。 ；2=store 尚未完成初始化。 ；3=当前已有支付进行中，拒绝重入。 ；4=商品 ID 在配置表中未找到。；其他渠道失败值按具体 Store 区分，ThirdPay 详见本表 nova_third_pay_failure_reason 属性。 Mobile：IAPMobileErrorCode：0=无错误。 ；1=配置表或平台商品中未找到目标商品。 ；2=订阅商品已处于有效订阅期内。 ；3=用户取消支付。 ；4=平台商店不可用或当前无法发起支付。 ；5=当前已有支付或验单流程正在进行。 ；6=网络不可用或网络请求失败。 ；7=服务端验单失败或拒绝订单。 ；8=MobileStore 初始化失败。 ；9=tableId / ReceiptParam / uid 超出平台透传参数的编码范围，为避免账号关联或业务数据被截断而拒绝支付。 ；1000=Unity IAP 当前不可购买。 ；1001=Unity IAP 已有待处理购买。 ；1002=Unity IAP 平台商品不可用。 ；1003=Unity IAP 签名校验失败。 ；1004=Unity IAP 用户取消购买。 ；1005=Unity IAP 支付被拒绝。 ；1006=Unity IAP 重复交易。 ；1007=Unity IAP 交易校验失败。 ；1008=Unity IAP 商店未连接。 ；1009=Unity IAP 平台未返回购买数据。 ；1010=Unity IAP 返回未知购买失败原因。 ；2000=验单前网络不可用。 ；2001=验单网络请求异常、HTTP 失败或响应包装失败。 ；2002=服务端响应中缺少本次请求对应的订单结果。 ；2003=服务端返回订单仍处于待校验或未完成状态。 ；2004=订单缺少验单所需凭据，例如 Google purchase token。 ；2005=服务端判定订单无效或拒绝订单。 ；2999=验单失败原因未知。。</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="n"/>
+      <c r="H32" s="16" t="n"/>
+      <c r="I32" s="16" t="n"/>
+    </row>
+    <row r="33">
       <c r="A33" s="7" t="n"/>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>nova_reason_detail</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>ThirdPay 失败原因中文描述，与 nova_third_pay_failure_reason 的枚举值一一对应。</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="n"/>
-      <c r="I33" s="7" t="n"/>
-    </row>
-    <row r="34" ht="14.5" customHeight="1" s="5">
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>具体 Store 或支付路由提供的补充诊断说明，不限于 ThirdPay。</t>
+        </is>
+      </c>
+      <c r="G33" s="16" t="n"/>
+      <c r="H33" s="16" t="n"/>
+      <c r="I33" s="16" t="n"/>
+    </row>
+    <row r="34">
       <c r="A34" s="7" t="n"/>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>nova_custom_data</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>业务层透传的自定义字符串参数。</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="7" t="n"/>
-    </row>
-    <row r="35" ht="14.5" customHeight="1" s="5">
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>仅业务透传字符串非空时附带；框架不解析。</t>
+        </is>
+      </c>
+      <c r="G34" s="16" t="n"/>
+      <c r="H34" s="16" t="n"/>
+      <c r="I34" s="16" t="n"/>
+    </row>
+    <row r="35">
       <c r="A35" s="7" t="n"/>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_open_mode</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 支付页实际打开方式：0=打开失败，1=Auth Tab，2=Custom Tabs，3=系统浏览器回退，4=嵌入式 WebView，5=iOS Safe Browsing。</t>
         </is>
       </c>
-      <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="n"/>
-      <c r="I35" s="7" t="n"/>
-    </row>
-    <row r="36" ht="14.5" customHeight="1" s="5">
+      <c r="G35" s="16" t="n"/>
+      <c r="H35" s="16" t="n"/>
+      <c r="I35" s="16" t="n"/>
+    </row>
+    <row r="36">
       <c r="A36" s="7" t="n"/>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_callback_status</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>pay_callback 状态：0=未收到或无法识别，1=支付成功，2=支付失败，3=支付成功但渠道信息尚未同步。</t>
         </is>
       </c>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n"/>
-      <c r="I36" s="7" t="n"/>
-    </row>
-    <row r="37" ht="14.5" customHeight="1" s="5">
+      <c r="G36" s="16" t="n"/>
+      <c r="H36" s="16" t="n"/>
+      <c r="I36" s="16" t="n"/>
+    </row>
+    <row r="37">
       <c r="A37" s="7" t="n"/>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_close_reason</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 关闭原因：0=未知，1=close_callback，2=嵌入式 WebView 关闭，3=iOS Safe Browsing 关闭，4=pay_callback 失败，5=未知 callback 状态，6=callback 参数无效，7=外部浏览器返回无成功 callback，8=callback 订单不匹配，9=验单开始后的迟到 callback，10=页面加载失败，11=Web 内容进程终止，12=页面异常，13=操作取消，14=会话被替换，15=Store 释放。</t>
         </is>
       </c>
-      <c r="G37" s="7" t="n"/>
-      <c r="H37" s="7" t="n"/>
-      <c r="I37" s="7" t="n"/>
-    </row>
-    <row r="38" ht="14.5" customHeight="1" s="5">
+      <c r="G37" s="16" t="n"/>
+      <c r="H37" s="16" t="n"/>
+      <c r="I37" s="16" t="n"/>
+    </row>
+    <row r="38">
       <c r="A38" s="7" t="n"/>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_failure_reason</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 支付/验单失败原因：0=未知，1=Store 禁用，2=Store 未初始化，3=重复支付，4=商品不存在，5=UID 缺失，6=支付配置不可用，7=服务端关闭支付，8=服务端未配置商品，9=WebView 服务不可用，10=外部浏览器服务不可用，11=Google 连接失败，12=Google token 创建失败，13=Google 支付 URL 构建失败，14=Google 用户取消，15=支付页打开失败，16=支付页打开异常，17=系统浏览器回退 URL 为空，18=callback 支付失败，19=callback 参数无效，20=callback 状态未知，21=callback 订单不匹配，22=callback 到达时已开始验单，23=外部浏览器返回无成功 callback，24=验单服务不可用，25=验单网络失败，26=验单响应缺少订单，27=服务端待支付，28=服务端处理中，29=服务端失败或过期，30=服务端订单不存在，31=未知服务端订单状态，32=操作取消，33=会话被替换，34=Store 释放，35=未分类异常，36=第三方支付 URL 构建失败，37=授权完成但支付 URL 缺失。</t>
         </is>
       </c>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="7" t="n"/>
-      <c r="I38" s="7" t="n"/>
-    </row>
-    <row r="39" ht="14.5" customHeight="1" s="5">
+      <c r="G38" s="16" t="n"/>
+      <c r="H38" s="16" t="n"/>
+      <c r="I38" s="16" t="n"/>
+    </row>
+    <row r="39">
       <c r="A39" s="7" t="n"/>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>nova_client_order_id</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
         <is>
           <t>客户端生成的 ThirdPay 订单号。</t>
         </is>
       </c>
-      <c r="G39" s="7" t="n"/>
-      <c r="H39" s="7" t="n"/>
-      <c r="I39" s="7" t="n"/>
-    </row>
-    <row r="40" ht="14.5" customHeight="1" s="5">
+      <c r="G39" s="16" t="n"/>
+      <c r="H39" s="16" t="n"/>
+      <c r="I39" s="16" t="n"/>
+    </row>
+    <row r="40">
       <c r="A40" s="7" t="n"/>
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>nova_server_order_id</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>服务端确认的 ThirdPay 订单号；无返回时为空。</t>
         </is>
       </c>
-      <c r="G40" s="7" t="n"/>
-      <c r="H40" s="7" t="n"/>
-      <c r="I40" s="7" t="n"/>
-    </row>
-    <row r="41" ht="14.5" customHeight="1" s="5">
+      <c r="G40" s="16" t="n"/>
+      <c r="H40" s="16" t="n"/>
+      <c r="I40" s="16" t="n"/>
+    </row>
+    <row r="41">
       <c r="A41" s="7" t="n"/>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>nova_native_error_code</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E41" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F41" s="16" t="inlineStr">
         <is>
           <t>支付页或原生能力返回的错误码；无错误时为 0。</t>
         </is>
       </c>
-      <c r="G41" s="7" t="n"/>
-      <c r="H41" s="7" t="n"/>
-      <c r="I41" s="7" t="n"/>
-    </row>
-    <row r="42" ht="14.5" customHeight="1" s="5">
+      <c r="G41" s="16" t="n"/>
+      <c r="H41" s="16" t="n"/>
+      <c r="I41" s="16" t="n"/>
+    </row>
+    <row r="42">
       <c r="A42" s="8" t="n"/>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>nova_native_error_message</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
         <is>
           <t>支付页或原生能力返回的错误描述。</t>
         </is>
       </c>
-      <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="n"/>
-      <c r="I42" s="8" t="n"/>
-    </row>
-    <row r="43" ht="14.5" customHeight="1" s="5">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="G42" s="16" t="n"/>
+      <c r="H42" s="16" t="n"/>
+      <c r="I42" s="16" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>nova_iap_validate_fail</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>验单失败</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C43" s="15" t="inlineStr">
         <is>
           <t>单轮服务端验单失败但订单仍可能重试或补单。</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>nova_table_id</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>商品配置表行 ID。</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>商品配置表行 ID；客户端使用 64 位整数。</t>
+        </is>
+      </c>
+      <c r="G43" s="16" t="inlineStr">
         <is>
           <t>单轮验单失败但订单仍保留时上报。</t>
         </is>
       </c>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="H43" s="16" t="inlineStr">
         <is>
           <t>tga</t>
         </is>
       </c>
-      <c r="I43" s="9" t="inlineStr">
+      <c r="I43" s="16" t="inlineStr">
         <is>
           <t>Mobile Store 的验单失败原因使用 IAPMobileErrorCode 的 2000 号段。</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="14.5" customHeight="1" s="5">
+    <row r="44">
       <c r="A44" s="7" t="n"/>
       <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>nova_product_id</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
         <is>
           <t>平台侧商品 ID。</t>
         </is>
       </c>
-      <c r="G44" s="7" t="n"/>
-      <c r="H44" s="7" t="n"/>
-      <c r="I44" s="7" t="n"/>
-    </row>
-    <row r="45" ht="14.5" customHeight="1" s="5">
+      <c r="G44" s="16" t="n"/>
+      <c r="H44" s="16" t="n"/>
+      <c r="I44" s="16" t="n"/>
+    </row>
+    <row r="45">
       <c r="A45" s="7" t="n"/>
       <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>nova_debug</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>是否测试模式。</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="n"/>
-      <c r="H45" s="7" t="n"/>
-      <c r="I45" s="7" t="n"/>
-    </row>
-    <row r="46" ht="14.5" customHeight="1" s="5">
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>是否 DevelopMode.Debug；不是 AlwaysPaySucceed。</t>
+        </is>
+      </c>
+      <c r="G45" s="16" t="n"/>
+      <c r="H45" s="16" t="n"/>
+      <c r="I45" s="16" t="n"/>
+    </row>
+    <row r="46">
       <c r="A46" s="7" t="n"/>
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>nova_price</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" s="16" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>商品本地化价格数值。</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="n"/>
-      <c r="H46" s="7" t="n"/>
-      <c r="I46" s="7" t="n"/>
-    </row>
-    <row r="47" ht="14.5" customHeight="1" s="5">
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>支付表 Price 配置解析的价格数值；不是平台本地化价格或可信实付金额。</t>
+        </is>
+      </c>
+      <c r="G46" s="16" t="n"/>
+      <c r="H46" s="16" t="n"/>
+      <c r="I46" s="16" t="n"/>
+    </row>
+    <row r="47">
       <c r="A47" s="7" t="n"/>
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>nova_channel</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>支付渠道名称。</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="n"/>
-      <c r="H47" s="7" t="n"/>
-      <c r="I47" s="7" t="n"/>
-    </row>
-    <row r="48" ht="14.5" customHeight="1" s="5">
+      <c r="E47" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>当前 Store 稳定渠道名；未找到 Store 时来自请求 StoreType，小写；空请求使用 router。</t>
+        </is>
+      </c>
+      <c r="G47" s="16" t="n"/>
+      <c r="H47" s="16" t="n"/>
+      <c r="I47" s="16" t="n"/>
+    </row>
+    <row r="48">
       <c r="A48" s="7" t="n"/>
       <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>nova_order_id</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="E48" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
         <is>
           <t>非 ThirdPay Store 的平台或服务端订单 ID；ThirdPay 不发送此字段，使用客户端/服务端双订单号。</t>
         </is>
       </c>
-      <c r="G48" s="7" t="n"/>
-      <c r="H48" s="7" t="n"/>
-      <c r="I48" s="7" t="n"/>
-    </row>
-    <row r="49" ht="14.5" customHeight="1" s="5">
+      <c r="G48" s="16" t="n"/>
+      <c r="H48" s="16" t="n"/>
+      <c r="I48" s="16" t="n"/>
+    </row>
+    <row r="49">
       <c r="A49" s="7" t="n"/>
       <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>nova_add_order</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F49" s="16" t="inlineStr">
         <is>
           <t>是否为恢复订单或补单订单。</t>
         </is>
       </c>
-      <c r="G49" s="7" t="n"/>
-      <c r="H49" s="7" t="n"/>
-      <c r="I49" s="7" t="n"/>
-    </row>
-    <row r="50" ht="14.5" customHeight="1" s="5">
+      <c r="G49" s="16" t="n"/>
+      <c r="H49" s="16" t="n"/>
+      <c r="I49" s="16" t="n"/>
+    </row>
+    <row r="50">
       <c r="A50" s="7" t="n"/>
       <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>nova_validate_count</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F50" s="16" t="inlineStr">
         <is>
           <t>当前验单尝试次数。</t>
         </is>
       </c>
-      <c r="G50" s="7" t="n"/>
-      <c r="H50" s="7" t="n"/>
-      <c r="I50" s="7" t="n"/>
-    </row>
-    <row r="51" ht="14.5" customHeight="1" s="5">
+      <c r="G50" s="16" t="n"/>
+      <c r="H50" s="16" t="n"/>
+      <c r="I50" s="16" t="n"/>
+    </row>
+    <row r="51">
       <c r="A51" s="7" t="n"/>
       <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="16" t="inlineStr">
         <is>
           <t>nova_net_error</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F51" s="16" t="inlineStr">
         <is>
           <t>是否为网络错误导致的失败。</t>
         </is>
       </c>
-      <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="n"/>
-      <c r="I51" s="7" t="n"/>
-    </row>
-    <row r="52" ht="14.5" customHeight="1" s="5">
+      <c r="G51" s="16" t="n"/>
+      <c r="H51" s="16" t="n"/>
+      <c r="I51" s="16" t="n"/>
+    </row>
+    <row r="52">
       <c r="A52" s="7" t="n"/>
       <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>nova_protocol_code</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F52" s="16" t="inlineStr">
         <is>
           <t>服务端返回的错误码。</t>
         </is>
       </c>
-      <c r="G52" s="7" t="n"/>
-      <c r="H52" s="7" t="n"/>
-      <c r="I52" s="7" t="n"/>
-    </row>
-    <row r="53" ht="14.5" customHeight="1" s="5">
+      <c r="G52" s="16" t="n"/>
+      <c r="H52" s="16" t="n"/>
+      <c r="I52" s="16" t="n"/>
+    </row>
+    <row r="53">
       <c r="A53" s="7" t="n"/>
       <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>nova_reason</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E53" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>失败原因枚举整数值。</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="n"/>
-      <c r="H53" s="7" t="n"/>
-      <c r="I53" s="7" t="n"/>
-    </row>
-    <row r="54" ht="24" customHeight="1" s="5">
+      <c r="F53" s="16" t="inlineStr">
+        <is>
+          <t>由具体 Store 写入失败原因整数；Mobile 使用 IAPMobileErrorCode，ThirdPay 使用本表 nova_third_pay_failure_reason 所列枚举。 Mobile：IAPMobileErrorCode：0=无错误。 ；1=配置表或平台商品中未找到目标商品。 ；2=订阅商品已处于有效订阅期内。 ；3=用户取消支付。 ；4=平台商店不可用或当前无法发起支付。 ；5=当前已有支付或验单流程正在进行。 ；6=网络不可用或网络请求失败。 ；7=服务端验单失败或拒绝订单。 ；8=MobileStore 初始化失败。 ；9=tableId / ReceiptParam / uid 超出平台透传参数的编码范围，为避免账号关联或业务数据被截断而拒绝支付。 ；1000=Unity IAP 当前不可购买。 ；1001=Unity IAP 已有待处理购买。 ；1002=Unity IAP 平台商品不可用。 ；1003=Unity IAP 签名校验失败。 ；1004=Unity IAP 用户取消购买。 ；1005=Unity IAP 支付被拒绝。 ；1006=Unity IAP 重复交易。 ；1007=Unity IAP 交易校验失败。 ；1008=Unity IAP 商店未连接。 ；1009=Unity IAP 平台未返回购买数据。 ；1010=Unity IAP 返回未知购买失败原因。 ；2000=验单前网络不可用。 ；2001=验单网络请求异常、HTTP 失败或响应包装失败。 ；2002=服务端响应中缺少本次请求对应的订单结果。 ；2003=服务端返回订单仍处于待校验或未完成状态。 ；2004=订单缺少验单所需凭据，例如 Google purchase token。 ；2005=服务端判定订单无效或拒绝订单。 ；2999=验单失败原因未知。。</t>
+        </is>
+      </c>
+      <c r="G53" s="16" t="n"/>
+      <c r="H53" s="16" t="n"/>
+      <c r="I53" s="16" t="n"/>
+    </row>
+    <row r="54">
       <c r="A54" s="7" t="n"/>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>nova_reason_detail</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>ThirdPay 失败原因中文描述，与 nova_third_pay_failure_reason 的枚举值一一对应。</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="n"/>
-      <c r="H54" s="7" t="n"/>
-      <c r="I54" s="7" t="n"/>
-    </row>
-    <row r="55" ht="14.5" customHeight="1" s="5">
+      <c r="E54" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>具体 Store 或支付路由提供的补充诊断说明，不限于 ThirdPay。</t>
+        </is>
+      </c>
+      <c r="G54" s="16" t="n"/>
+      <c r="H54" s="16" t="n"/>
+      <c r="I54" s="16" t="n"/>
+    </row>
+    <row r="55">
       <c r="A55" s="7" t="n"/>
       <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" s="16" t="inlineStr">
         <is>
           <t>nova_custom_data</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>业务层透传的自定义字符串参数。</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="n"/>
-      <c r="H55" s="7" t="n"/>
-      <c r="I55" s="7" t="n"/>
-    </row>
-    <row r="56" ht="14.5" customHeight="1" s="5">
+      <c r="E55" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F55" s="16" t="inlineStr">
+        <is>
+          <t>仅业务透传字符串非空时附带；框架不解析。</t>
+        </is>
+      </c>
+      <c r="G55" s="16" t="n"/>
+      <c r="H55" s="16" t="n"/>
+      <c r="I55" s="16" t="n"/>
+    </row>
+    <row r="56">
       <c r="A56" s="7" t="n"/>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>nova_protocol_message</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="E56" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F56" s="16" t="inlineStr">
         <is>
           <t>服务端返回的错误信息描述。</t>
         </is>
       </c>
-      <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="n"/>
-      <c r="I56" s="7" t="n"/>
-    </row>
-    <row r="57" ht="14.5" customHeight="1" s="5">
+      <c r="G56" s="16" t="n"/>
+      <c r="H56" s="16" t="n"/>
+      <c r="I56" s="16" t="n"/>
+    </row>
+    <row r="57">
       <c r="A57" s="7" t="n"/>
       <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" s="16" t="inlineStr">
         <is>
           <t>nova_validation_scene</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F57" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 验单场景：0=未知，1=应用内成功 callback，2=应用内支付页模糊返回，3=新支付前预检，4=启动或后台补单，5=外部浏览器返回兜底，6=外部浏览器成功 callback。</t>
         </is>
       </c>
-      <c r="G57" s="7" t="n"/>
-      <c r="H57" s="7" t="n"/>
-      <c r="I57" s="7" t="n"/>
-    </row>
-    <row r="58" ht="14.5" customHeight="1" s="5">
+      <c r="G57" s="16" t="n"/>
+      <c r="H57" s="16" t="n"/>
+      <c r="I57" s="16" t="n"/>
+    </row>
+    <row r="58">
       <c r="A58" s="7" t="n"/>
       <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>nova_server_order_status</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E58" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F58" s="16" t="inlineStr">
         <is>
           <t>服务端 PbNetThirdVerifyOrderStatus：0=未指定或无有效响应，1=待支付，2=支付中，3=已支付，4=失败或过期，5=已发货，6=订单不存在。</t>
         </is>
       </c>
-      <c r="G58" s="7" t="n"/>
-      <c r="H58" s="7" t="n"/>
-      <c r="I58" s="7" t="n"/>
-    </row>
-    <row r="59" ht="14.5" customHeight="1" s="5">
+      <c r="G58" s="16" t="n"/>
+      <c r="H58" s="16" t="n"/>
+      <c r="I58" s="16" t="n"/>
+    </row>
+    <row r="59">
       <c r="A59" s="7" t="n"/>
       <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D59" s="16" t="inlineStr">
         <is>
           <t>nova_client_order_status</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E59" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F59" s="16" t="inlineStr">
         <is>
           <t>客户端归一化订单状态：0=未知，1=已支付可发货，2=已发货，3=待支付，4=处理中，5=失败或过期，6=不存在，7=响应缺单，8=网络失败，9=验单服务不可用，10=未知服务端状态。</t>
         </is>
       </c>
-      <c r="G59" s="7" t="n"/>
-      <c r="H59" s="7" t="n"/>
-      <c r="I59" s="7" t="n"/>
-    </row>
-    <row r="60" ht="14.5" customHeight="1" s="5">
+      <c r="G59" s="16" t="n"/>
+      <c r="H59" s="16" t="n"/>
+      <c r="I59" s="16" t="n"/>
+    </row>
+    <row r="60">
       <c r="A60" s="7" t="n"/>
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D60" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_failure_reason</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E60" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F60" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 支付/验单失败原因：0=未知，1=Store 禁用，2=Store 未初始化，3=重复支付，4=商品不存在，5=UID 缺失，6=支付配置不可用，7=服务端关闭支付，8=服务端未配置商品，9=WebView 服务不可用，10=外部浏览器服务不可用，11=Google 连接失败，12=Google token 创建失败，13=Google 支付 URL 构建失败，14=Google 用户取消，15=支付页打开失败，16=支付页打开异常，17=系统浏览器回退 URL 为空，18=callback 支付失败，19=callback 参数无效，20=callback 状态未知，21=callback 订单不匹配，22=callback 到达时已开始验单，23=外部浏览器返回无成功 callback，24=验单服务不可用，25=验单网络失败，26=验单响应缺少订单，27=服务端待支付，28=服务端处理中，29=服务端失败或过期，30=服务端订单不存在，31=未知服务端订单状态，32=操作取消，33=会话被替换，34=Store 释放，35=未分类异常，36=第三方支付 URL 构建失败，37=授权完成但支付 URL 缺失。</t>
         </is>
       </c>
-      <c r="G60" s="7" t="n"/>
-      <c r="H60" s="7" t="n"/>
-      <c r="I60" s="7" t="n"/>
-    </row>
-    <row r="61" ht="14.5" customHeight="1" s="5">
+      <c r="G60" s="16" t="n"/>
+      <c r="H60" s="16" t="n"/>
+      <c r="I60" s="16" t="n"/>
+    </row>
+    <row r="61">
       <c r="A61" s="7" t="n"/>
       <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D61" s="16" t="inlineStr">
         <is>
           <t>nova_client_order_id</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="E61" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F61" s="16" t="inlineStr">
         <is>
           <t>客户端生成的 ThirdPay 订单号。</t>
         </is>
       </c>
-      <c r="G61" s="7" t="n"/>
-      <c r="H61" s="7" t="n"/>
-      <c r="I61" s="7" t="n"/>
-    </row>
-    <row r="62" ht="14.5" customHeight="1" s="5">
+      <c r="G61" s="16" t="n"/>
+      <c r="H61" s="16" t="n"/>
+      <c r="I61" s="16" t="n"/>
+    </row>
+    <row r="62">
       <c r="A62" s="8" t="n"/>
       <c r="B62" s="8" t="n"/>
       <c r="C62" s="8" t="n"/>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" s="16" t="inlineStr">
         <is>
           <t>nova_server_order_id</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="E62" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F62" s="16" t="inlineStr">
         <is>
           <t>服务端确认的 ThirdPay 订单号；无返回时为空。</t>
         </is>
       </c>
-      <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="8" t="n"/>
-    </row>
-    <row r="63" ht="14.5" customHeight="1" s="5">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="G62" s="16" t="n"/>
+      <c r="H62" s="16" t="n"/>
+      <c r="I62" s="16" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="inlineStr">
         <is>
           <t>nova_iap_validate_fail_finish</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>验单最终失败</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C63" s="15" t="inlineStr">
         <is>
           <t>服务端验单最终失败或超出重试次数。</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D63" s="16" t="inlineStr">
         <is>
           <t>nova_table_id</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>商品配置表行 ID。</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
+      <c r="E63" s="16" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F63" s="16" t="inlineStr">
+        <is>
+          <t>商品配置表行 ID；客户端使用 64 位整数。</t>
+        </is>
+      </c>
+      <c r="G63" s="16" t="inlineStr">
         <is>
           <t>无效订单或超出重试后进入最终失败时上报。</t>
         </is>
       </c>
-      <c r="H63" s="6" t="inlineStr">
+      <c r="H63" s="16" t="inlineStr">
         <is>
           <t>tga</t>
         </is>
       </c>
-      <c r="I63" s="6" t="inlineStr">
+      <c r="I63" s="16" t="inlineStr">
         <is>
           <t>服务端协议错误信息写入 protocol 字段，主失败分类仍写入 nova_reason。</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="14.5" customHeight="1" s="5">
+    <row r="64">
       <c r="A64" s="7" t="n"/>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>nova_product_id</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="E64" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F64" s="16" t="inlineStr">
         <is>
           <t>平台侧商品 ID。</t>
         </is>
       </c>
-      <c r="G64" s="7" t="n"/>
-      <c r="H64" s="7" t="n"/>
-      <c r="I64" s="7" t="n"/>
-    </row>
-    <row r="65" ht="14.5" customHeight="1" s="5">
+      <c r="G64" s="16" t="n"/>
+      <c r="H64" s="16" t="n"/>
+      <c r="I64" s="16" t="n"/>
+    </row>
+    <row r="65">
       <c r="A65" s="7" t="n"/>
       <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D65" s="16" t="inlineStr">
         <is>
           <t>nova_debug</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E65" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>是否测试模式。</t>
-        </is>
-      </c>
-      <c r="G65" s="7" t="n"/>
-      <c r="H65" s="7" t="n"/>
-      <c r="I65" s="7" t="n"/>
-    </row>
-    <row r="66" ht="14.5" customHeight="1" s="5">
+      <c r="F65" s="16" t="inlineStr">
+        <is>
+          <t>是否 DevelopMode.Debug；不是 AlwaysPaySucceed。</t>
+        </is>
+      </c>
+      <c r="G65" s="16" t="n"/>
+      <c r="H65" s="16" t="n"/>
+      <c r="I65" s="16" t="n"/>
+    </row>
+    <row r="66">
       <c r="A66" s="7" t="n"/>
       <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D66" s="16" t="inlineStr">
         <is>
           <t>nova_price</t>
         </is>
       </c>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="E66" s="16" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>商品本地化价格数值。</t>
-        </is>
-      </c>
-      <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="n"/>
-      <c r="I66" s="7" t="n"/>
-    </row>
-    <row r="67" ht="14.5" customHeight="1" s="5">
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>支付表 Price 配置解析的价格数值；不是平台本地化价格或可信实付金额。</t>
+        </is>
+      </c>
+      <c r="G66" s="16" t="n"/>
+      <c r="H66" s="16" t="n"/>
+      <c r="I66" s="16" t="n"/>
+    </row>
+    <row r="67">
       <c r="A67" s="7" t="n"/>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D67" s="16" t="inlineStr">
         <is>
           <t>nova_channel</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>支付渠道名称。</t>
-        </is>
-      </c>
-      <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="n"/>
-      <c r="I67" s="7" t="n"/>
-    </row>
-    <row r="68" ht="14.5" customHeight="1" s="5">
+      <c r="E67" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F67" s="16" t="inlineStr">
+        <is>
+          <t>当前 Store 稳定渠道名；未找到 Store 时来自请求 StoreType，小写；空请求使用 router。</t>
+        </is>
+      </c>
+      <c r="G67" s="16" t="n"/>
+      <c r="H67" s="16" t="n"/>
+      <c r="I67" s="16" t="n"/>
+    </row>
+    <row r="68">
       <c r="A68" s="7" t="n"/>
       <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D68" s="16" t="inlineStr">
         <is>
           <t>nova_order_id</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="E68" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F68" s="16" t="inlineStr">
         <is>
           <t>非 ThirdPay Store 的平台或服务端订单 ID；ThirdPay 不发送此字段，使用客户端/服务端双订单号。</t>
         </is>
       </c>
-      <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="n"/>
-      <c r="I68" s="7" t="n"/>
-    </row>
-    <row r="69" ht="14.5" customHeight="1" s="5">
+      <c r="G68" s="16" t="n"/>
+      <c r="H68" s="16" t="n"/>
+      <c r="I68" s="16" t="n"/>
+    </row>
+    <row r="69">
       <c r="A69" s="7" t="n"/>
       <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D69" s="16" t="inlineStr">
         <is>
           <t>nova_add_order</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E69" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F69" s="16" t="inlineStr">
         <is>
           <t>是否为恢复订单或补单订单。</t>
         </is>
       </c>
-      <c r="G69" s="7" t="n"/>
-      <c r="H69" s="7" t="n"/>
-      <c r="I69" s="7" t="n"/>
-    </row>
-    <row r="70" ht="14.5" customHeight="1" s="5">
+      <c r="G69" s="16" t="n"/>
+      <c r="H69" s="16" t="n"/>
+      <c r="I69" s="16" t="n"/>
+    </row>
+    <row r="70">
       <c r="A70" s="7" t="n"/>
       <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D70" s="16" t="inlineStr">
         <is>
           <t>nova_validate_count</t>
         </is>
       </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="E70" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr">
+      <c r="F70" s="16" t="inlineStr">
         <is>
           <t>当前验单尝试次数。</t>
         </is>
       </c>
-      <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
-      <c r="I70" s="7" t="n"/>
-    </row>
-    <row r="71" ht="14.5" customHeight="1" s="5">
+      <c r="G70" s="16" t="n"/>
+      <c r="H70" s="16" t="n"/>
+      <c r="I70" s="16" t="n"/>
+    </row>
+    <row r="71">
       <c r="A71" s="7" t="n"/>
       <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D71" s="16" t="inlineStr">
         <is>
           <t>nova_net_error</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E71" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F71" s="16" t="inlineStr">
         <is>
           <t>是否为网络错误导致的失败。</t>
         </is>
       </c>
-      <c r="G71" s="7" t="n"/>
-      <c r="H71" s="7" t="n"/>
-      <c r="I71" s="7" t="n"/>
-    </row>
-    <row r="72" ht="14.5" customHeight="1" s="5">
+      <c r="G71" s="16" t="n"/>
+      <c r="H71" s="16" t="n"/>
+      <c r="I71" s="16" t="n"/>
+    </row>
+    <row r="72">
       <c r="A72" s="7" t="n"/>
       <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D72" s="16" t="inlineStr">
         <is>
           <t>nova_protocol_code</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="E72" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="F72" s="16" t="inlineStr">
         <is>
           <t>服务端返回的错误码。</t>
         </is>
       </c>
-      <c r="G72" s="7" t="n"/>
-      <c r="H72" s="7" t="n"/>
-      <c r="I72" s="7" t="n"/>
-    </row>
-    <row r="73" ht="14.5" customHeight="1" s="5">
+      <c r="G72" s="16" t="n"/>
+      <c r="H72" s="16" t="n"/>
+      <c r="I72" s="16" t="n"/>
+    </row>
+    <row r="73">
       <c r="A73" s="7" t="n"/>
       <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D73" s="16" t="inlineStr">
         <is>
           <t>nova_protocol_message</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="E73" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F73" s="16" t="inlineStr">
         <is>
           <t>服务端返回的错误信息描述。</t>
         </is>
       </c>
-      <c r="G73" s="7" t="n"/>
-      <c r="H73" s="7" t="n"/>
-      <c r="I73" s="7" t="n"/>
-    </row>
-    <row r="74" ht="14.5" customHeight="1" s="5">
+      <c r="G73" s="16" t="n"/>
+      <c r="H73" s="16" t="n"/>
+      <c r="I73" s="16" t="n"/>
+    </row>
+    <row r="74">
       <c r="A74" s="7" t="n"/>
       <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>nova_reason</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="E74" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>失败原因枚举整数值。</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="n"/>
-      <c r="H74" s="7" t="n"/>
-      <c r="I74" s="7" t="n"/>
-    </row>
-    <row r="75" ht="14.5" customHeight="1" s="5">
+      <c r="F74" s="16" t="inlineStr">
+        <is>
+          <t>由具体 Store 写入失败原因整数；Mobile 使用 IAPMobileErrorCode，ThirdPay 使用本表 nova_third_pay_failure_reason 所列枚举。 Mobile：IAPMobileErrorCode：0=无错误。 ；1=配置表或平台商品中未找到目标商品。 ；2=订阅商品已处于有效订阅期内。 ；3=用户取消支付。 ；4=平台商店不可用或当前无法发起支付。 ；5=当前已有支付或验单流程正在进行。 ；6=网络不可用或网络请求失败。 ；7=服务端验单失败或拒绝订单。 ；8=MobileStore 初始化失败。 ；9=tableId / ReceiptParam / uid 超出平台透传参数的编码范围，为避免账号关联或业务数据被截断而拒绝支付。 ；1000=Unity IAP 当前不可购买。 ；1001=Unity IAP 已有待处理购买。 ；1002=Unity IAP 平台商品不可用。 ；1003=Unity IAP 签名校验失败。 ；1004=Unity IAP 用户取消购买。 ；1005=Unity IAP 支付被拒绝。 ；1006=Unity IAP 重复交易。 ；1007=Unity IAP 交易校验失败。 ；1008=Unity IAP 商店未连接。 ；1009=Unity IAP 平台未返回购买数据。 ；1010=Unity IAP 返回未知购买失败原因。 ；2000=验单前网络不可用。 ；2001=验单网络请求异常、HTTP 失败或响应包装失败。 ；2002=服务端响应中缺少本次请求对应的订单结果。 ；2003=服务端返回订单仍处于待校验或未完成状态。 ；2004=订单缺少验单所需凭据，例如 Google purchase token。 ；2005=服务端判定订单无效或拒绝订单。 ；2999=验单失败原因未知。。</t>
+        </is>
+      </c>
+      <c r="G74" s="16" t="n"/>
+      <c r="H74" s="16" t="n"/>
+      <c r="I74" s="16" t="n"/>
+    </row>
+    <row r="75">
       <c r="A75" s="7" t="n"/>
       <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D75" s="16" t="inlineStr">
         <is>
           <t>nova_reason_detail</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>ThirdPay 失败原因中文描述，与 nova_third_pay_failure_reason 的枚举值一一对应。</t>
-        </is>
-      </c>
-      <c r="G75" s="7" t="n"/>
-      <c r="H75" s="7" t="n"/>
-      <c r="I75" s="7" t="n"/>
-    </row>
-    <row r="76" ht="14.5" customHeight="1" s="5">
+      <c r="E75" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F75" s="16" t="inlineStr">
+        <is>
+          <t>具体 Store 或支付路由提供的补充诊断说明，不限于 ThirdPay。</t>
+        </is>
+      </c>
+      <c r="G75" s="16" t="n"/>
+      <c r="H75" s="16" t="n"/>
+      <c r="I75" s="16" t="n"/>
+    </row>
+    <row r="76">
       <c r="A76" s="7" t="n"/>
       <c r="B76" s="7" t="n"/>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D76" s="16" t="inlineStr">
         <is>
           <t>nova_custom_data</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>业务层透传的自定义字符串参数。</t>
-        </is>
-      </c>
-      <c r="G76" s="7" t="n"/>
-      <c r="H76" s="7" t="n"/>
-      <c r="I76" s="7" t="n"/>
-    </row>
-    <row r="77" ht="14.5" customHeight="1" s="5">
+      <c r="E76" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F76" s="16" t="inlineStr">
+        <is>
+          <t>仅业务透传字符串非空时附带；框架不解析。</t>
+        </is>
+      </c>
+      <c r="G76" s="16" t="n"/>
+      <c r="H76" s="16" t="n"/>
+      <c r="I76" s="16" t="n"/>
+    </row>
+    <row r="77">
       <c r="A77" s="7" t="n"/>
       <c r="B77" s="7" t="n"/>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D77" s="16" t="inlineStr">
         <is>
           <t>nova_validation_scene</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="E77" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr">
+      <c r="F77" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 验单场景：0=未知，1=应用内成功 callback，2=应用内支付页模糊返回，3=新支付前预检，4=启动或后台补单，5=外部浏览器返回兜底，6=外部浏览器成功 callback。</t>
         </is>
       </c>
-      <c r="G77" s="7" t="n"/>
-      <c r="H77" s="7" t="n"/>
-      <c r="I77" s="7" t="n"/>
-    </row>
-    <row r="78" ht="14.5" customHeight="1" s="5">
+      <c r="G77" s="16" t="n"/>
+      <c r="H77" s="16" t="n"/>
+      <c r="I77" s="16" t="n"/>
+    </row>
+    <row r="78">
       <c r="A78" s="7" t="n"/>
       <c r="B78" s="7" t="n"/>
       <c r="C78" s="7" t="n"/>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D78" s="16" t="inlineStr">
         <is>
           <t>nova_server_order_status</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="E78" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="F78" s="16" t="inlineStr">
         <is>
           <t>服务端 PbNetThirdVerifyOrderStatus：0=未指定或无有效响应，1=待支付，2=支付中，3=已支付，4=失败或过期，5=已发货，6=订单不存在。</t>
         </is>
       </c>
-      <c r="G78" s="7" t="n"/>
-      <c r="H78" s="7" t="n"/>
-      <c r="I78" s="7" t="n"/>
-    </row>
-    <row r="79" ht="14.5" customHeight="1" s="5">
+      <c r="G78" s="16" t="n"/>
+      <c r="H78" s="16" t="n"/>
+      <c r="I78" s="16" t="n"/>
+    </row>
+    <row r="79">
       <c r="A79" s="7" t="n"/>
       <c r="B79" s="7" t="n"/>
       <c r="C79" s="7" t="n"/>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D79" s="16" t="inlineStr">
         <is>
           <t>nova_client_order_status</t>
         </is>
       </c>
-      <c r="E79" s="3" t="inlineStr">
+      <c r="E79" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
+      <c r="F79" s="16" t="inlineStr">
         <is>
           <t>客户端归一化订单状态：0=未知，1=已支付可发货，2=已发货，3=待支付，4=处理中，5=失败或过期，6=不存在，7=响应缺单，8=网络失败，9=验单服务不可用，10=未知服务端状态。</t>
         </is>
       </c>
-      <c r="G79" s="7" t="n"/>
-      <c r="H79" s="7" t="n"/>
-      <c r="I79" s="7" t="n"/>
-    </row>
-    <row r="80" ht="14.5" customHeight="1" s="5">
+      <c r="G79" s="16" t="n"/>
+      <c r="H79" s="16" t="n"/>
+      <c r="I79" s="16" t="n"/>
+    </row>
+    <row r="80">
       <c r="A80" s="7" t="n"/>
       <c r="B80" s="7" t="n"/>
       <c r="C80" s="7" t="n"/>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D80" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_failure_reason</t>
         </is>
       </c>
-      <c r="E80" s="3" t="inlineStr">
+      <c r="E80" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F80" s="3" t="inlineStr">
+      <c r="F80" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 支付/验单失败原因：0=未知，1=Store 禁用，2=Store 未初始化，3=重复支付，4=商品不存在，5=UID 缺失，6=支付配置不可用，7=服务端关闭支付，8=服务端未配置商品，9=WebView 服务不可用，10=外部浏览器服务不可用，11=Google 连接失败，12=Google token 创建失败，13=Google 支付 URL 构建失败，14=Google 用户取消，15=支付页打开失败，16=支付页打开异常，17=系统浏览器回退 URL 为空，18=callback 支付失败，19=callback 参数无效，20=callback 状态未知，21=callback 订单不匹配，22=callback 到达时已开始验单，23=外部浏览器返回无成功 callback，24=验单服务不可用，25=验单网络失败，26=验单响应缺少订单，27=服务端待支付，28=服务端处理中，29=服务端失败或过期，30=服务端订单不存在，31=未知服务端订单状态，32=操作取消，33=会话被替换，34=Store 释放，35=未分类异常，36=第三方支付 URL 构建失败，37=授权完成但支付 URL 缺失。</t>
         </is>
       </c>
-      <c r="G80" s="7" t="n"/>
-      <c r="H80" s="7" t="n"/>
-      <c r="I80" s="7" t="n"/>
-    </row>
-    <row r="81" ht="14.5" customHeight="1" s="5">
+      <c r="G80" s="16" t="n"/>
+      <c r="H80" s="16" t="n"/>
+      <c r="I80" s="16" t="n"/>
+    </row>
+    <row r="81">
       <c r="A81" s="7" t="n"/>
       <c r="B81" s="7" t="n"/>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="D81" s="16" t="inlineStr">
         <is>
           <t>nova_client_order_id</t>
         </is>
       </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
+      <c r="E81" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F81" s="16" t="inlineStr">
         <is>
           <t>客户端生成的 ThirdPay 订单号。</t>
         </is>
       </c>
-      <c r="G81" s="7" t="n"/>
-      <c r="H81" s="7" t="n"/>
-      <c r="I81" s="7" t="n"/>
-    </row>
-    <row r="82" ht="14.5" customHeight="1" s="5">
+      <c r="G81" s="16" t="n"/>
+      <c r="H81" s="16" t="n"/>
+      <c r="I81" s="16" t="n"/>
+    </row>
+    <row r="82">
       <c r="A82" s="8" t="n"/>
       <c r="B82" s="8" t="n"/>
       <c r="C82" s="8" t="n"/>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="D82" s="16" t="inlineStr">
         <is>
           <t>nova_server_order_id</t>
         </is>
       </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="inlineStr">
+      <c r="E82" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F82" s="16" t="inlineStr">
         <is>
           <t>服务端确认的 ThirdPay 订单号；无返回时为空。</t>
         </is>
       </c>
-      <c r="G82" s="8" t="n"/>
-      <c r="H82" s="8" t="n"/>
-      <c r="I82" s="8" t="n"/>
-    </row>
-    <row r="83" ht="14.5" customHeight="1" s="5">
-      <c r="A83" s="9" t="inlineStr">
+      <c r="G82" s="16" t="n"/>
+      <c r="H82" s="16" t="n"/>
+      <c r="I82" s="16" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="inlineStr">
         <is>
           <t>nova_iap_validate_success</t>
         </is>
       </c>
-      <c r="B83" s="9" t="inlineStr">
+      <c r="B83" s="14" t="inlineStr">
         <is>
           <t>验单成功</t>
         </is>
       </c>
-      <c r="C83" s="9" t="inlineStr">
+      <c r="C83" s="15" t="inlineStr">
         <is>
           <t>服务端验单成功并终结订单。</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D83" s="16" t="inlineStr">
         <is>
           <t>nova_table_id</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>商品配置表行 ID。</t>
-        </is>
-      </c>
-      <c r="G83" s="9" t="inlineStr">
+      <c r="E83" s="16" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F83" s="16" t="inlineStr">
+        <is>
+          <t>商品配置表行 ID；客户端使用 64 位整数。</t>
+        </is>
+      </c>
+      <c r="G83" s="16" t="inlineStr">
         <is>
           <t>服务端返回已验证、已发货或已补发时上报。</t>
         </is>
       </c>
-      <c r="H83" s="9" t="inlineStr">
+      <c r="H83" s="16" t="inlineStr">
         <is>
           <t>tga</t>
         </is>
       </c>
-      <c r="I83" s="9" t="inlineStr">
+      <c r="I83" s="16" t="inlineStr">
         <is>
           <t>Mobile Store 优先使用服务端验单响应的订单 ID，缺失时回退当前运行期交易 ID。</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="14.5" customHeight="1" s="5">
+    <row r="84">
       <c r="A84" s="7" t="n"/>
       <c r="B84" s="7" t="n"/>
       <c r="C84" s="7" t="n"/>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D84" s="16" t="inlineStr">
         <is>
           <t>nova_product_id</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="E84" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F84" s="16" t="inlineStr">
         <is>
           <t>平台侧商品 ID。</t>
         </is>
       </c>
-      <c r="G84" s="7" t="n"/>
-      <c r="H84" s="7" t="n"/>
-      <c r="I84" s="7" t="n"/>
-    </row>
-    <row r="85" ht="14.5" customHeight="1" s="5">
+      <c r="G84" s="16" t="n"/>
+      <c r="H84" s="16" t="n"/>
+      <c r="I84" s="16" t="n"/>
+    </row>
+    <row r="85">
       <c r="A85" s="7" t="n"/>
       <c r="B85" s="7" t="n"/>
       <c r="C85" s="7" t="n"/>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D85" s="16" t="inlineStr">
         <is>
           <t>nova_debug</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E85" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>是否测试模式。</t>
-        </is>
-      </c>
-      <c r="G85" s="7" t="n"/>
-      <c r="H85" s="7" t="n"/>
-      <c r="I85" s="7" t="n"/>
-    </row>
-    <row r="86" ht="14.5" customHeight="1" s="5">
+      <c r="F85" s="16" t="inlineStr">
+        <is>
+          <t>是否 DevelopMode.Debug；不是 AlwaysPaySucceed。</t>
+        </is>
+      </c>
+      <c r="G85" s="16" t="n"/>
+      <c r="H85" s="16" t="n"/>
+      <c r="I85" s="16" t="n"/>
+    </row>
+    <row r="86">
       <c r="A86" s="7" t="n"/>
       <c r="B86" s="7" t="n"/>
       <c r="C86" s="7" t="n"/>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D86" s="16" t="inlineStr">
         <is>
           <t>nova_price</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E86" s="16" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>商品本地化价格数值。</t>
-        </is>
-      </c>
-      <c r="G86" s="7" t="n"/>
-      <c r="H86" s="7" t="n"/>
-      <c r="I86" s="7" t="n"/>
-    </row>
-    <row r="87" ht="14.5" customHeight="1" s="5">
+      <c r="F86" s="16" t="inlineStr">
+        <is>
+          <t>支付表 Price 配置解析的价格数值；不是平台本地化价格或可信实付金额。</t>
+        </is>
+      </c>
+      <c r="G86" s="16" t="n"/>
+      <c r="H86" s="16" t="n"/>
+      <c r="I86" s="16" t="n"/>
+    </row>
+    <row r="87">
       <c r="A87" s="7" t="n"/>
       <c r="B87" s="7" t="n"/>
       <c r="C87" s="7" t="n"/>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D87" s="16" t="inlineStr">
         <is>
           <t>nova_channel</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>支付渠道名称。</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="n"/>
-      <c r="H87" s="7" t="n"/>
-      <c r="I87" s="7" t="n"/>
-    </row>
-    <row r="88" ht="14.5" customHeight="1" s="5">
+      <c r="E87" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F87" s="16" t="inlineStr">
+        <is>
+          <t>当前 Store 稳定渠道名；未找到 Store 时来自请求 StoreType，小写；空请求使用 router。</t>
+        </is>
+      </c>
+      <c r="G87" s="16" t="n"/>
+      <c r="H87" s="16" t="n"/>
+      <c r="I87" s="16" t="n"/>
+    </row>
+    <row r="88">
       <c r="A88" s="7" t="n"/>
       <c r="B88" s="7" t="n"/>
       <c r="C88" s="7" t="n"/>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D88" s="16" t="inlineStr">
         <is>
           <t>nova_order_id</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="E88" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F88" s="16" t="inlineStr">
         <is>
           <t>非 ThirdPay Store 的平台或服务端订单 ID；ThirdPay 不发送此字段，使用客户端/服务端双订单号。</t>
         </is>
       </c>
-      <c r="G88" s="7" t="n"/>
-      <c r="H88" s="7" t="n"/>
-      <c r="I88" s="7" t="n"/>
-    </row>
-    <row r="89" ht="14.5" customHeight="1" s="5">
+      <c r="G88" s="16" t="n"/>
+      <c r="H88" s="16" t="n"/>
+      <c r="I88" s="16" t="n"/>
+    </row>
+    <row r="89">
       <c r="A89" s="7" t="n"/>
       <c r="B89" s="7" t="n"/>
       <c r="C89" s="7" t="n"/>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="D89" s="16" t="inlineStr">
         <is>
           <t>nova_add_order</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E89" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F89" s="16" t="inlineStr">
         <is>
           <t>是否为恢复订单或补单订单。</t>
         </is>
       </c>
-      <c r="G89" s="7" t="n"/>
-      <c r="H89" s="7" t="n"/>
-      <c r="I89" s="7" t="n"/>
-    </row>
-    <row r="90" ht="14.5" customHeight="1" s="5">
+      <c r="G89" s="16" t="n"/>
+      <c r="H89" s="16" t="n"/>
+      <c r="I89" s="16" t="n"/>
+    </row>
+    <row r="90">
       <c r="A90" s="7" t="n"/>
       <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="D90" s="16" t="inlineStr">
         <is>
           <t>nova_validate_count</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E90" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F90" s="16" t="inlineStr">
         <is>
           <t>当前验单尝试次数。</t>
         </is>
       </c>
-      <c r="G90" s="7" t="n"/>
-      <c r="H90" s="7" t="n"/>
-      <c r="I90" s="7" t="n"/>
-    </row>
-    <row r="91" ht="14.5" customHeight="1" s="5">
+      <c r="G90" s="16" t="n"/>
+      <c r="H90" s="16" t="n"/>
+      <c r="I90" s="16" t="n"/>
+    </row>
+    <row r="91">
       <c r="A91" s="7" t="n"/>
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="D91" s="16" t="inlineStr">
         <is>
           <t>nova_custom_data</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>业务层透传的自定义字符串参数。</t>
-        </is>
-      </c>
-      <c r="G91" s="7" t="n"/>
-      <c r="H91" s="7" t="n"/>
-      <c r="I91" s="7" t="n"/>
-    </row>
-    <row r="92" ht="14.5" customHeight="1" s="5">
+      <c r="E91" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F91" s="16" t="inlineStr">
+        <is>
+          <t>仅业务透传字符串非空时附带；框架不解析。</t>
+        </is>
+      </c>
+      <c r="G91" s="16" t="n"/>
+      <c r="H91" s="16" t="n"/>
+      <c r="I91" s="16" t="n"/>
+    </row>
+    <row r="92">
       <c r="A92" s="7" t="n"/>
       <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D92" s="16" t="inlineStr">
         <is>
           <t>nova_validation_scene</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E92" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F92" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 验单场景：0=未知，1=应用内成功 callback，2=应用内支付页模糊返回，3=新支付前预检，4=启动或后台补单，5=外部浏览器返回兜底，6=外部浏览器成功 callback。</t>
         </is>
       </c>
-      <c r="G92" s="7" t="n"/>
-      <c r="H92" s="7" t="n"/>
-      <c r="I92" s="7" t="n"/>
-    </row>
-    <row r="93" ht="14.5" customHeight="1" s="5">
+      <c r="G92" s="16" t="n"/>
+      <c r="H92" s="16" t="n"/>
+      <c r="I92" s="16" t="n"/>
+    </row>
+    <row r="93">
       <c r="A93" s="7" t="n"/>
       <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="D93" s="16" t="inlineStr">
         <is>
           <t>nova_server_order_status</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E93" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F93" s="16" t="inlineStr">
         <is>
           <t>服务端 PbNetThirdVerifyOrderStatus：0=未指定或无有效响应，1=待支付，2=支付中，3=已支付，4=失败或过期，5=已发货，6=订单不存在。</t>
         </is>
       </c>
-      <c r="G93" s="7" t="n"/>
-      <c r="H93" s="7" t="n"/>
-      <c r="I93" s="7" t="n"/>
-    </row>
-    <row r="94" ht="14.5" customHeight="1" s="5">
+      <c r="G93" s="16" t="n"/>
+      <c r="H93" s="16" t="n"/>
+      <c r="I93" s="16" t="n"/>
+    </row>
+    <row r="94">
       <c r="A94" s="7" t="n"/>
       <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="D94" s="16" t="inlineStr">
         <is>
           <t>nova_client_order_status</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E94" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F94" s="16" t="inlineStr">
         <is>
           <t>客户端归一化订单状态：0=未知，1=已支付可发货，2=已发货，3=待支付，4=处理中，5=失败或过期，6=不存在，7=响应缺单，8=网络失败，9=验单服务不可用，10=未知服务端状态。</t>
         </is>
       </c>
-      <c r="G94" s="7" t="n"/>
-      <c r="H94" s="7" t="n"/>
-      <c r="I94" s="7" t="n"/>
-    </row>
-    <row r="95" ht="14.5" customHeight="1" s="5">
+      <c r="G94" s="16" t="n"/>
+      <c r="H94" s="16" t="n"/>
+      <c r="I94" s="16" t="n"/>
+    </row>
+    <row r="95">
       <c r="A95" s="7" t="n"/>
       <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="D95" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_failure_reason</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E95" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F95" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 支付/验单失败原因：0=未知，1=Store 禁用，2=Store 未初始化，3=重复支付，4=商品不存在，5=UID 缺失，6=支付配置不可用，7=服务端关闭支付，8=服务端未配置商品，9=WebView 服务不可用，10=外部浏览器服务不可用，11=Google 连接失败，12=Google token 创建失败，13=Google 支付 URL 构建失败，14=Google 用户取消，15=支付页打开失败，16=支付页打开异常，17=系统浏览器回退 URL 为空，18=callback 支付失败，19=callback 参数无效，20=callback 状态未知，21=callback 订单不匹配，22=callback 到达时已开始验单，23=外部浏览器返回无成功 callback，24=验单服务不可用，25=验单网络失败，26=验单响应缺少订单，27=服务端待支付，28=服务端处理中，29=服务端失败或过期，30=服务端订单不存在，31=未知服务端订单状态，32=操作取消，33=会话被替换，34=Store 释放，35=未分类异常，36=第三方支付 URL 构建失败，37=授权完成但支付 URL 缺失。</t>
         </is>
       </c>
-      <c r="G95" s="7" t="n"/>
-      <c r="H95" s="7" t="n"/>
-      <c r="I95" s="7" t="n"/>
-    </row>
-    <row r="96" ht="14.5" customHeight="1" s="5">
+      <c r="G95" s="16" t="n"/>
+      <c r="H95" s="16" t="n"/>
+      <c r="I95" s="16" t="n"/>
+    </row>
+    <row r="96">
       <c r="A96" s="7" t="n"/>
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="D96" s="16" t="inlineStr">
         <is>
           <t>nova_protocol_code</t>
         </is>
       </c>
-      <c r="E96" s="3" t="inlineStr">
+      <c r="E96" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F96" s="3" t="inlineStr">
+      <c r="F96" s="16" t="inlineStr">
         <is>
           <t>服务端返回的错误码。</t>
         </is>
       </c>
-      <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="n"/>
-      <c r="I96" s="7" t="n"/>
-    </row>
-    <row r="97" ht="14.5" customHeight="1" s="5">
+      <c r="G96" s="16" t="n"/>
+      <c r="H96" s="16" t="n"/>
+      <c r="I96" s="16" t="n"/>
+    </row>
+    <row r="97">
       <c r="A97" s="7" t="n"/>
       <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="3" t="inlineStr">
+      <c r="D97" s="16" t="inlineStr">
         <is>
           <t>nova_protocol_message</t>
         </is>
       </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
+      <c r="E97" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F97" s="16" t="inlineStr">
         <is>
           <t>服务端返回的错误信息描述。</t>
         </is>
       </c>
-      <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="n"/>
-      <c r="I97" s="7" t="n"/>
-    </row>
-    <row r="98" ht="14.5" customHeight="1" s="5">
+      <c r="G97" s="16" t="n"/>
+      <c r="H97" s="16" t="n"/>
+      <c r="I97" s="16" t="n"/>
+    </row>
+    <row r="98">
       <c r="A98" s="7" t="n"/>
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D98" s="16" t="inlineStr">
         <is>
           <t>nova_client_order_id</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="E98" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F98" s="16" t="inlineStr">
         <is>
           <t>客户端生成的 ThirdPay 订单号。</t>
         </is>
       </c>
-      <c r="G98" s="7" t="n"/>
-      <c r="H98" s="7" t="n"/>
-      <c r="I98" s="7" t="n"/>
-    </row>
-    <row r="99" ht="14.5" customHeight="1" s="5">
+      <c r="G98" s="16" t="n"/>
+      <c r="H98" s="16" t="n"/>
+      <c r="I98" s="16" t="n"/>
+    </row>
+    <row r="99">
       <c r="A99" s="8" t="n"/>
       <c r="B99" s="8" t="n"/>
       <c r="C99" s="8" t="n"/>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="D99" s="16" t="inlineStr">
         <is>
           <t>nova_server_order_id</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="E99" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F99" s="16" t="inlineStr">
         <is>
           <t>服务端确认的 ThirdPay 订单号；无返回时为空。</t>
         </is>
       </c>
-      <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="n"/>
-      <c r="I99" s="8" t="n"/>
-    </row>
-    <row r="100" ht="14.5" customHeight="1" s="5">
-      <c r="A100" s="6" t="inlineStr">
+      <c r="G99" s="16" t="n"/>
+      <c r="H99" s="16" t="n"/>
+      <c r="I99" s="16" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="14" t="inlineStr">
         <is>
           <t>nova_iap_first_pay_order_validate</t>
         </is>
       </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="B100" s="14" t="inlineStr">
         <is>
           <t>首次支付订单验单失败</t>
         </is>
       </c>
-      <c r="C100" s="6" t="inlineStr">
+      <c r="C100" s="15" t="inlineStr">
         <is>
           <t>当前主动支付订单第一次验单失败。</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="D100" s="16" t="inlineStr">
         <is>
           <t>nova_table_id</t>
         </is>
       </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="inlineStr">
-        <is>
-          <t>商品配置表行 ID。</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
+      <c r="E100" s="16" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F100" s="16" t="inlineStr">
+        <is>
+          <t>商品配置表行 ID；客户端使用 64 位整数。</t>
+        </is>
+      </c>
+      <c r="G100" s="16" t="inlineStr">
         <is>
           <t>当前主动支付订单第一次验单失败时上报。</t>
         </is>
       </c>
-      <c r="H100" s="6" t="inlineStr">
+      <c r="H100" s="16" t="inlineStr">
         <is>
           <t>tga</t>
         </is>
       </c>
-      <c r="I100" s="6" t="inlineStr">
+      <c r="I100" s="16" t="inlineStr">
         <is>
           <t>用于区分首验失败和后续重试失败。</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="14.5" customHeight="1" s="5">
+    <row r="101">
       <c r="A101" s="7" t="n"/>
       <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="D101" s="16" t="inlineStr">
         <is>
           <t>nova_product_id</t>
         </is>
       </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="inlineStr">
+      <c r="E101" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F101" s="16" t="inlineStr">
         <is>
           <t>平台侧商品 ID。</t>
         </is>
       </c>
-      <c r="G101" s="7" t="n"/>
-      <c r="H101" s="7" t="n"/>
-      <c r="I101" s="7" t="n"/>
-    </row>
-    <row r="102" ht="14.5" customHeight="1" s="5">
+      <c r="G101" s="16" t="n"/>
+      <c r="H101" s="16" t="n"/>
+      <c r="I101" s="16" t="n"/>
+    </row>
+    <row r="102">
       <c r="A102" s="7" t="n"/>
       <c r="B102" s="7" t="n"/>
       <c r="C102" s="7" t="n"/>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="D102" s="16" t="inlineStr">
         <is>
           <t>nova_debug</t>
         </is>
       </c>
-      <c r="E102" s="3" t="inlineStr">
+      <c r="E102" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t>是否测试模式。</t>
-        </is>
-      </c>
-      <c r="G102" s="7" t="n"/>
-      <c r="H102" s="7" t="n"/>
-      <c r="I102" s="7" t="n"/>
-    </row>
-    <row r="103" ht="14.5" customHeight="1" s="5">
+      <c r="F102" s="16" t="inlineStr">
+        <is>
+          <t>是否 DevelopMode.Debug；不是 AlwaysPaySucceed。</t>
+        </is>
+      </c>
+      <c r="G102" s="16" t="n"/>
+      <c r="H102" s="16" t="n"/>
+      <c r="I102" s="16" t="n"/>
+    </row>
+    <row r="103">
       <c r="A103" s="7" t="n"/>
       <c r="B103" s="7" t="n"/>
       <c r="C103" s="7" t="n"/>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="D103" s="16" t="inlineStr">
         <is>
           <t>nova_price</t>
         </is>
       </c>
-      <c r="E103" s="3" t="inlineStr">
+      <c r="E103" s="16" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F103" s="3" t="inlineStr">
-        <is>
-          <t>商品本地化价格数值。</t>
-        </is>
-      </c>
-      <c r="G103" s="7" t="n"/>
-      <c r="H103" s="7" t="n"/>
-      <c r="I103" s="7" t="n"/>
-    </row>
-    <row r="104" ht="14.5" customHeight="1" s="5">
+      <c r="F103" s="16" t="inlineStr">
+        <is>
+          <t>支付表 Price 配置解析的价格数值；不是平台本地化价格或可信实付金额。</t>
+        </is>
+      </c>
+      <c r="G103" s="16" t="n"/>
+      <c r="H103" s="16" t="n"/>
+      <c r="I103" s="16" t="n"/>
+    </row>
+    <row r="104">
       <c r="A104" s="7" t="n"/>
       <c r="B104" s="7" t="n"/>
       <c r="C104" s="7" t="n"/>
-      <c r="D104" s="3" t="inlineStr">
+      <c r="D104" s="16" t="inlineStr">
         <is>
           <t>nova_channel</t>
         </is>
       </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="inlineStr">
-        <is>
-          <t>支付渠道名称。</t>
-        </is>
-      </c>
-      <c r="G104" s="7" t="n"/>
-      <c r="H104" s="7" t="n"/>
-      <c r="I104" s="7" t="n"/>
-    </row>
-    <row r="105" ht="14.5" customHeight="1" s="5">
+      <c r="E104" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F104" s="16" t="inlineStr">
+        <is>
+          <t>当前 Store 稳定渠道名；未找到 Store 时来自请求 StoreType，小写；空请求使用 router。</t>
+        </is>
+      </c>
+      <c r="G104" s="16" t="n"/>
+      <c r="H104" s="16" t="n"/>
+      <c r="I104" s="16" t="n"/>
+    </row>
+    <row r="105">
       <c r="A105" s="7" t="n"/>
       <c r="B105" s="7" t="n"/>
       <c r="C105" s="7" t="n"/>
-      <c r="D105" s="3" t="inlineStr">
+      <c r="D105" s="16" t="inlineStr">
         <is>
           <t>nova_order_id</t>
         </is>
       </c>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F105" s="3" t="inlineStr">
+      <c r="E105" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F105" s="16" t="inlineStr">
         <is>
           <t>非 ThirdPay Store 的平台或服务端订单 ID；ThirdPay 不发送此字段，使用客户端/服务端双订单号。</t>
         </is>
       </c>
-      <c r="G105" s="7" t="n"/>
-      <c r="H105" s="7" t="n"/>
-      <c r="I105" s="7" t="n"/>
-    </row>
-    <row r="106" ht="14.5" customFormat="1" customHeight="1" s="4">
+      <c r="G105" s="16" t="n"/>
+      <c r="H105" s="16" t="n"/>
+      <c r="I105" s="16" t="n"/>
+    </row>
+    <row r="106">
       <c r="A106" s="7" t="n"/>
       <c r="B106" s="7" t="n"/>
       <c r="C106" s="7" t="n"/>
-      <c r="D106" s="3" t="inlineStr">
+      <c r="D106" s="16" t="inlineStr">
         <is>
           <t>nova_client_order_id</t>
         </is>
       </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F106" s="3" t="inlineStr">
+      <c r="E106" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F106" s="16" t="inlineStr">
         <is>
           <t>客户端生成的 ThirdPay 订单号。</t>
         </is>
       </c>
-      <c r="G106" s="7" t="n"/>
-      <c r="H106" s="7" t="n"/>
-      <c r="I106" s="7" t="n"/>
-    </row>
-    <row r="107" ht="14.5" customFormat="1" customHeight="1" s="4">
+      <c r="G106" s="16" t="n"/>
+      <c r="H106" s="16" t="n"/>
+      <c r="I106" s="16" t="n"/>
+    </row>
+    <row r="107">
       <c r="A107" s="7" t="n"/>
       <c r="B107" s="7" t="n"/>
       <c r="C107" s="7" t="n"/>
-      <c r="D107" s="3" t="inlineStr">
+      <c r="D107" s="16" t="inlineStr">
         <is>
           <t>nova_server_order_id</t>
         </is>
       </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="inlineStr">
+      <c r="E107" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F107" s="16" t="inlineStr">
         <is>
           <t>服务端确认的 ThirdPay 订单号；首次验单失败尚未取得时为空。</t>
         </is>
       </c>
-      <c r="G107" s="7" t="n"/>
-      <c r="H107" s="7" t="n"/>
-      <c r="I107" s="7" t="n"/>
-    </row>
-    <row r="108" ht="14.5" customHeight="1" s="5">
+      <c r="G107" s="16" t="n"/>
+      <c r="H107" s="16" t="n"/>
+      <c r="I107" s="16" t="n"/>
+    </row>
+    <row r="108">
       <c r="A108" s="7" t="n"/>
       <c r="B108" s="7" t="n"/>
       <c r="C108" s="7" t="n"/>
-      <c r="D108" s="3" t="inlineStr">
+      <c r="D108" s="16" t="inlineStr">
         <is>
           <t>nova_add_order</t>
         </is>
       </c>
-      <c r="E108" s="3" t="inlineStr">
+      <c r="E108" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F108" s="3" t="inlineStr">
+      <c r="F108" s="16" t="inlineStr">
         <is>
           <t>是否为恢复订单或补单订单。</t>
         </is>
       </c>
-      <c r="G108" s="7" t="n"/>
-      <c r="H108" s="7" t="n"/>
-      <c r="I108" s="7" t="n"/>
-    </row>
-    <row r="109" ht="14.5" customHeight="1" s="5">
+      <c r="G108" s="16" t="n"/>
+      <c r="H108" s="16" t="n"/>
+      <c r="I108" s="16" t="n"/>
+    </row>
+    <row r="109">
       <c r="A109" s="7" t="n"/>
       <c r="B109" s="7" t="n"/>
       <c r="C109" s="7" t="n"/>
-      <c r="D109" s="3" t="inlineStr">
+      <c r="D109" s="16" t="inlineStr">
         <is>
           <t>nova_validate_count</t>
         </is>
       </c>
-      <c r="E109" s="3" t="inlineStr">
+      <c r="E109" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F109" s="3" t="inlineStr">
+      <c r="F109" s="16" t="inlineStr">
         <is>
           <t>当前验单尝试次数。</t>
         </is>
       </c>
-      <c r="G109" s="7" t="n"/>
-      <c r="H109" s="7" t="n"/>
-      <c r="I109" s="7" t="n"/>
-    </row>
-    <row r="110" ht="24" customHeight="1" s="5">
+      <c r="G109" s="16" t="n"/>
+      <c r="H109" s="16" t="n"/>
+      <c r="I109" s="16" t="n"/>
+    </row>
+    <row r="110">
       <c r="A110" s="7" t="n"/>
       <c r="B110" s="7" t="n"/>
       <c r="C110" s="7" t="n"/>
-      <c r="D110" s="3" t="inlineStr">
+      <c r="D110" s="16" t="inlineStr">
         <is>
           <t>nova_net_error</t>
         </is>
       </c>
-      <c r="E110" s="3" t="inlineStr">
+      <c r="E110" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F110" s="3" t="inlineStr">
+      <c r="F110" s="16" t="inlineStr">
         <is>
           <t>是否为网络错误导致的失败。</t>
         </is>
       </c>
-      <c r="G110" s="7" t="n"/>
-      <c r="H110" s="7" t="n"/>
-      <c r="I110" s="7" t="n"/>
-    </row>
-    <row r="111" ht="24" customHeight="1" s="5">
+      <c r="G110" s="16" t="n"/>
+      <c r="H110" s="16" t="n"/>
+      <c r="I110" s="16" t="n"/>
+    </row>
+    <row r="111">
       <c r="A111" s="8" t="n"/>
       <c r="B111" s="8" t="n"/>
       <c r="C111" s="8" t="n"/>
-      <c r="D111" s="3" t="inlineStr">
+      <c r="D111" s="16" t="inlineStr">
         <is>
           <t>nova_custom_data</t>
         </is>
       </c>
-      <c r="E111" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F111" s="3" t="inlineStr">
-        <is>
-          <t>业务层透传的自定义字符串参数。</t>
-        </is>
-      </c>
-      <c r="G111" s="8" t="n"/>
-      <c r="H111" s="8" t="n"/>
-      <c r="I111" s="8" t="n"/>
-    </row>
-    <row r="112" ht="14.5" customHeight="1" s="5">
-      <c r="A112" s="9" t="inlineStr">
+      <c r="E111" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F111" s="16" t="inlineStr">
+        <is>
+          <t>仅业务透传字符串非空时附带；框架不解析。</t>
+        </is>
+      </c>
+      <c r="G111" s="16" t="n"/>
+      <c r="H111" s="16" t="n"/>
+      <c r="I111" s="16" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="14" t="inlineStr">
         <is>
           <t>nova_iap_deliver_fail</t>
         </is>
       </c>
-      <c r="B112" s="9" t="inlineStr">
+      <c r="B112" s="14" t="inlineStr">
         <is>
           <t>发货失败</t>
         </is>
       </c>
-      <c r="C112" s="9" t="inlineStr">
-        <is>
-          <t>验单已成功但业务发货失败。</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="C112" s="15" t="inlineStr">
+        <is>
+          <t>预留事件常量；当前仓内没有实际发起调用。</t>
+        </is>
+      </c>
+      <c r="D112" s="16" t="inlineStr">
         <is>
           <t>nova_product_id</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="E112" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F112" s="16" t="inlineStr">
         <is>
           <t>平台侧商品 ID。</t>
         </is>
       </c>
-      <c r="G112" s="9" t="inlineStr">
-        <is>
-          <t>验单成功后发货失败时上报。</t>
-        </is>
-      </c>
-      <c r="H112" s="9" t="inlineStr">
+      <c r="G112" s="16" t="inlineStr">
+        <is>
+          <t>当前未触发。</t>
+        </is>
+      </c>
+      <c r="H112" s="16" t="inlineStr">
         <is>
           <t>tga</t>
         </is>
       </c>
-      <c r="I112" s="9" t="inlineStr">
-        <is>
-          <t>Mobile 官方内购当前不触发该事件。</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="14.5" customHeight="1" s="5">
+      <c r="I112" s="16" t="inlineStr">
+        <is>
+          <t>预留约定，不能据此推断运行时已上报。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
       <c r="A113" s="7" t="n"/>
       <c r="B113" s="7" t="n"/>
       <c r="C113" s="7" t="n"/>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="D113" s="16" t="inlineStr">
         <is>
           <t>nova_debug</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E113" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>是否测试模式。</t>
-        </is>
-      </c>
-      <c r="G113" s="7" t="n"/>
-      <c r="H113" s="7" t="n"/>
-      <c r="I113" s="7" t="n"/>
-    </row>
-    <row r="114" ht="24" customHeight="1" s="5">
+      <c r="F113" s="16" t="inlineStr">
+        <is>
+          <t>是否 DevelopMode.Debug；不是 AlwaysPaySucceed。</t>
+        </is>
+      </c>
+      <c r="G113" s="16" t="n"/>
+      <c r="H113" s="16" t="n"/>
+      <c r="I113" s="16" t="n"/>
+    </row>
+    <row r="114">
       <c r="A114" s="7" t="n"/>
       <c r="B114" s="7" t="n"/>
       <c r="C114" s="7" t="n"/>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="D114" s="16" t="inlineStr">
         <is>
           <t>nova_order_id</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="E114" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F114" s="16" t="inlineStr">
         <is>
           <t>平台或服务端订单 ID。</t>
         </is>
       </c>
-      <c r="G114" s="7" t="n"/>
-      <c r="H114" s="7" t="n"/>
-      <c r="I114" s="7" t="n"/>
-    </row>
-    <row r="115" ht="14.5" customHeight="1" s="5">
+      <c r="G114" s="16" t="n"/>
+      <c r="H114" s="16" t="n"/>
+      <c r="I114" s="16" t="n"/>
+    </row>
+    <row r="115">
       <c r="A115" s="8" t="n"/>
       <c r="B115" s="8" t="n"/>
       <c r="C115" s="8" t="n"/>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="D115" s="16" t="inlineStr">
         <is>
           <t>nova_custom_data</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>业务层透传的自定义字符串参数。</t>
-        </is>
-      </c>
-      <c r="G115" s="8" t="n"/>
-      <c r="H115" s="8" t="n"/>
-      <c r="I115" s="8" t="n"/>
-    </row>
-    <row r="116" ht="14.5" customHeight="1" s="5">
-      <c r="A116" s="6" t="inlineStr">
+      <c r="E115" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F115" s="16" t="inlineStr">
+        <is>
+          <t>仅业务透传字符串非空时附带；框架不解析。</t>
+        </is>
+      </c>
+      <c r="G115" s="16" t="n"/>
+      <c r="H115" s="16" t="n"/>
+      <c r="I115" s="16" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="14" t="inlineStr">
         <is>
           <t>nova_iap_create_order_fail</t>
         </is>
       </c>
-      <c r="B116" s="6" t="inlineStr">
+      <c r="B116" s="14" t="inlineStr">
         <is>
           <t>创建第三方订单失败</t>
         </is>
       </c>
-      <c r="C116" s="6" t="inlineStr">
+      <c r="C116" s="15" t="inlineStr">
         <is>
           <t>第三方支付订单创建失败。</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr">
+      <c r="D116" s="16" t="inlineStr">
         <is>
           <t>nova_table_id</t>
         </is>
       </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t>商品配置表行 ID。</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr">
+      <c r="E116" s="16" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F116" s="16" t="inlineStr">
+        <is>
+          <t>商品配置表行 ID；客户端使用 64 位整数。</t>
+        </is>
+      </c>
+      <c r="G116" s="16" t="inlineStr">
         <is>
           <t>第三方订单创建失败时上报。</t>
         </is>
       </c>
-      <c r="H116" s="6" t="inlineStr">
+      <c r="H116" s="16" t="inlineStr">
         <is>
           <t>tga</t>
         </is>
       </c>
-      <c r="I116" s="6" t="inlineStr">
+      <c r="I116" s="16" t="inlineStr">
         <is>
           <t>Mobile 官方内购不触发该事件。</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="14.5" customHeight="1" s="5">
+    <row r="117">
       <c r="A117" s="7" t="n"/>
       <c r="B117" s="7" t="n"/>
       <c r="C117" s="7" t="n"/>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="D117" s="16" t="inlineStr">
         <is>
           <t>nova_product_id</t>
         </is>
       </c>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F117" s="3" t="inlineStr">
+      <c r="E117" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F117" s="16" t="inlineStr">
         <is>
           <t>平台侧商品 ID。</t>
         </is>
       </c>
-      <c r="G117" s="7" t="n"/>
-      <c r="H117" s="7" t="n"/>
-      <c r="I117" s="7" t="n"/>
-    </row>
-    <row r="118" ht="14.5" customHeight="1" s="5">
+      <c r="G117" s="16" t="n"/>
+      <c r="H117" s="16" t="n"/>
+      <c r="I117" s="16" t="n"/>
+    </row>
+    <row r="118">
       <c r="A118" s="7" t="n"/>
       <c r="B118" s="7" t="n"/>
       <c r="C118" s="7" t="n"/>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="D118" s="16" t="inlineStr">
         <is>
           <t>nova_debug</t>
         </is>
       </c>
-      <c r="E118" s="3" t="inlineStr">
+      <c r="E118" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t>是否测试模式。</t>
-        </is>
-      </c>
-      <c r="G118" s="7" t="n"/>
-      <c r="H118" s="7" t="n"/>
-      <c r="I118" s="7" t="n"/>
-    </row>
-    <row r="119" ht="14.5" customHeight="1" s="5">
+      <c r="F118" s="16" t="inlineStr">
+        <is>
+          <t>是否 DevelopMode.Debug；不是 AlwaysPaySucceed。</t>
+        </is>
+      </c>
+      <c r="G118" s="16" t="n"/>
+      <c r="H118" s="16" t="n"/>
+      <c r="I118" s="16" t="n"/>
+    </row>
+    <row r="119">
       <c r="A119" s="7" t="n"/>
       <c r="B119" s="7" t="n"/>
       <c r="C119" s="7" t="n"/>
-      <c r="D119" s="3" t="inlineStr">
+      <c r="D119" s="16" t="inlineStr">
         <is>
           <t>nova_price</t>
         </is>
       </c>
-      <c r="E119" s="3" t="inlineStr">
+      <c r="E119" s="16" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F119" s="3" t="inlineStr">
-        <is>
-          <t>商品本地化价格数值。</t>
-        </is>
-      </c>
-      <c r="G119" s="7" t="n"/>
-      <c r="H119" s="7" t="n"/>
-      <c r="I119" s="7" t="n"/>
-    </row>
-    <row r="120" ht="14.5" customHeight="1" s="5">
+      <c r="F119" s="16" t="inlineStr">
+        <is>
+          <t>支付表 Price 配置解析的价格数值；不是平台本地化价格或可信实付金额。</t>
+        </is>
+      </c>
+      <c r="G119" s="16" t="n"/>
+      <c r="H119" s="16" t="n"/>
+      <c r="I119" s="16" t="n"/>
+    </row>
+    <row r="120">
       <c r="A120" s="7" t="n"/>
       <c r="B120" s="7" t="n"/>
       <c r="C120" s="7" t="n"/>
-      <c r="D120" s="3" t="inlineStr">
+      <c r="D120" s="16" t="inlineStr">
         <is>
           <t>nova_channel</t>
         </is>
       </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t>支付渠道名称。</t>
-        </is>
-      </c>
-      <c r="G120" s="7" t="n"/>
-      <c r="H120" s="7" t="n"/>
-      <c r="I120" s="7" t="n"/>
-    </row>
-    <row r="121" ht="14.5" customHeight="1" s="5">
+      <c r="E120" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F120" s="16" t="inlineStr">
+        <is>
+          <t>固定为 thirdpay。</t>
+        </is>
+      </c>
+      <c r="G120" s="16" t="n"/>
+      <c r="H120" s="16" t="n"/>
+      <c r="I120" s="16" t="n"/>
+    </row>
+    <row r="121">
       <c r="A121" s="7" t="n"/>
       <c r="B121" s="7" t="n"/>
       <c r="C121" s="7" t="n"/>
-      <c r="D121" s="3" t="inlineStr">
+      <c r="D121" s="16" t="inlineStr">
         <is>
           <t>nova_reason</t>
         </is>
       </c>
-      <c r="E121" s="3" t="inlineStr">
+      <c r="E121" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>失败原因枚举整数值。</t>
-        </is>
-      </c>
-      <c r="G121" s="7" t="n"/>
-      <c r="H121" s="7" t="n"/>
-      <c r="I121" s="7" t="n"/>
-    </row>
-    <row r="122" ht="14.5" customHeight="1" s="5">
+      <c r="F121" s="16" t="inlineStr">
+        <is>
+          <t>IAPThirdPayErrorCode：0=无错误。 ；1=Store 尚未完成初始化。 ；2=用户主动取消支付。 ；3=支付网络请求失败。 ；4=服务端验单失败。 ；5=第三方支付 Store 当前不可用。 ；6=应用内支付页关闭或打开失败。 ；7=Google 外部结算能力尚未就绪。 ；8=订单需要业务侧手动发货。 ；9=服务端订单仍在处理中。。</t>
+        </is>
+      </c>
+      <c r="G121" s="16" t="n"/>
+      <c r="H121" s="16" t="n"/>
+      <c r="I121" s="16" t="n"/>
+    </row>
+    <row r="122">
       <c r="A122" s="7" t="n"/>
       <c r="B122" s="7" t="n"/>
       <c r="C122" s="7" t="n"/>
-      <c r="D122" s="3" t="inlineStr">
+      <c r="D122" s="16" t="inlineStr">
         <is>
           <t>nova_reason_detail</t>
         </is>
       </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F122" s="3" t="inlineStr">
+      <c r="E122" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F122" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 创建订单失败原因中文描述，与 nova_third_pay_create_failure_reason 的枚举值一一对应。</t>
         </is>
       </c>
-      <c r="G122" s="7" t="n"/>
-      <c r="H122" s="7" t="n"/>
-      <c r="I122" s="7" t="n"/>
-    </row>
-    <row r="123" ht="14.5" customHeight="1" s="5">
+      <c r="G122" s="16" t="n"/>
+      <c r="H122" s="16" t="n"/>
+      <c r="I122" s="16" t="n"/>
+    </row>
+    <row r="123">
       <c r="A123" s="7" t="n"/>
       <c r="B123" s="7" t="n"/>
       <c r="C123" s="7" t="n"/>
-      <c r="D123" s="3" t="inlineStr">
+      <c r="D123" s="16" t="inlineStr">
         <is>
           <t>nova_net_error</t>
         </is>
       </c>
-      <c r="E123" s="3" t="inlineStr">
+      <c r="E123" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F123" s="3" t="inlineStr">
+      <c r="F123" s="16" t="inlineStr">
         <is>
           <t>是否为网络错误导致的失败。</t>
         </is>
       </c>
-      <c r="G123" s="7" t="n"/>
-      <c r="H123" s="7" t="n"/>
-      <c r="I123" s="7" t="n"/>
-    </row>
-    <row r="124" ht="14.5" customHeight="1" s="5">
+      <c r="G123" s="16" t="n"/>
+      <c r="H123" s="16" t="n"/>
+      <c r="I123" s="16" t="n"/>
+    </row>
+    <row r="124">
       <c r="A124" s="7" t="n"/>
       <c r="B124" s="7" t="n"/>
       <c r="C124" s="7" t="n"/>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="D124" s="16" t="inlineStr">
         <is>
           <t>nova_custom_data</t>
         </is>
       </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="inlineStr">
-        <is>
-          <t>业务层透传的自定义字符串参数。</t>
-        </is>
-      </c>
-      <c r="G124" s="7" t="n"/>
-      <c r="H124" s="7" t="n"/>
-      <c r="I124" s="7" t="n"/>
-    </row>
-    <row r="125" ht="14.5" customHeight="1" s="5">
+      <c r="E124" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F124" s="16" t="inlineStr">
+        <is>
+          <t>仅业务透传字符串非空时附带；框架不解析。</t>
+        </is>
+      </c>
+      <c r="G124" s="16" t="n"/>
+      <c r="H124" s="16" t="n"/>
+      <c r="I124" s="16" t="n"/>
+    </row>
+    <row r="125">
       <c r="A125" s="7" t="n"/>
       <c r="B125" s="7" t="n"/>
       <c r="C125" s="7" t="n"/>
-      <c r="D125" s="3" t="inlineStr">
+      <c r="D125" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_create_failure_reason</t>
         </is>
       </c>
-      <c r="E125" s="3" t="inlineStr">
+      <c r="E125" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F125" s="3" t="inlineStr">
+      <c r="F125" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 创建订单失败原因：0=未知，1=UID 缺失，2=支付配置不可用，3=服务端关闭支付，4=服务端未配置商品，5=支付页服务不可用，6=Google 连接失败，7=Google token 创建失败，8=Google 支付 URL 构建失败，9=Google 用户取消，10=支付 URL 构建异常，11=支付 URL 为空。</t>
         </is>
       </c>
-      <c r="G125" s="7" t="n"/>
-      <c r="H125" s="7" t="n"/>
-      <c r="I125" s="7" t="n"/>
-    </row>
-    <row r="126" ht="14.5" customHeight="1" s="5">
+      <c r="G125" s="16" t="n"/>
+      <c r="H125" s="16" t="n"/>
+      <c r="I125" s="16" t="n"/>
+    </row>
+    <row r="126">
       <c r="A126" s="7" t="n"/>
       <c r="B126" s="7" t="n"/>
       <c r="C126" s="7" t="n"/>
-      <c r="D126" s="3" t="inlineStr">
+      <c r="D126" s="16" t="inlineStr">
         <is>
           <t>nova_client_order_id</t>
         </is>
       </c>
-      <c r="E126" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F126" s="3" t="inlineStr">
+      <c r="E126" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F126" s="16" t="inlineStr">
         <is>
           <t>已生成但未完成创建流程的客户端订单号。</t>
         </is>
       </c>
-      <c r="G126" s="7" t="n"/>
-      <c r="H126" s="7" t="n"/>
-      <c r="I126" s="7" t="n"/>
-    </row>
-    <row r="127" ht="14.5" customHeight="1" s="5">
+      <c r="G126" s="16" t="n"/>
+      <c r="H126" s="16" t="n"/>
+      <c r="I126" s="16" t="n"/>
+    </row>
+    <row r="127">
       <c r="A127" s="7" t="n"/>
       <c r="B127" s="7" t="n"/>
       <c r="C127" s="7" t="n"/>
-      <c r="D127" s="3" t="inlineStr">
+      <c r="D127" s="16" t="inlineStr">
         <is>
           <t>nova_server_order_id</t>
         </is>
       </c>
-      <c r="E127" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F127" s="3" t="inlineStr">
+      <c r="E127" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F127" s="16" t="inlineStr">
         <is>
           <t>服务端确认的 ThirdPay 订单号；创建失败阶段通常未取得，发送空字符串。</t>
         </is>
       </c>
-      <c r="G127" s="7" t="n"/>
-      <c r="H127" s="7" t="n"/>
-      <c r="I127" s="7" t="n"/>
-    </row>
-    <row r="128" ht="24" customHeight="1" s="5">
+      <c r="G127" s="16" t="n"/>
+      <c r="H127" s="16" t="n"/>
+      <c r="I127" s="16" t="n"/>
+    </row>
+    <row r="128">
       <c r="A128" s="7" t="n"/>
       <c r="B128" s="7" t="n"/>
       <c r="C128" s="7" t="n"/>
-      <c r="D128" s="3" t="inlineStr">
+      <c r="D128" s="16" t="inlineStr">
         <is>
           <t>nova_native_error_code</t>
         </is>
       </c>
-      <c r="E128" s="3" t="inlineStr">
+      <c r="E128" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F128" s="3" t="inlineStr">
+      <c r="F128" s="16" t="inlineStr">
         <is>
           <t>原生或服务端补充错误码；无错误时为 0。</t>
         </is>
       </c>
-      <c r="G128" s="7" t="n"/>
-      <c r="H128" s="7" t="n"/>
-      <c r="I128" s="7" t="n"/>
-    </row>
-    <row r="129" ht="24" customHeight="1" s="5">
+      <c r="G128" s="16" t="n"/>
+      <c r="H128" s="16" t="n"/>
+      <c r="I128" s="16" t="n"/>
+    </row>
+    <row r="129">
       <c r="A129" s="8" t="n"/>
       <c r="B129" s="8" t="n"/>
       <c r="C129" s="8" t="n"/>
-      <c r="D129" s="3" t="inlineStr">
+      <c r="D129" s="16" t="inlineStr">
         <is>
           <t>nova_native_error_message</t>
         </is>
       </c>
-      <c r="E129" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F129" s="3" t="inlineStr">
+      <c r="E129" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F129" s="16" t="inlineStr">
         <is>
           <t>原生或服务端补充错误描述。</t>
         </is>
       </c>
-      <c r="G129" s="8" t="n"/>
-      <c r="H129" s="8" t="n"/>
-      <c r="I129" s="8" t="n"/>
-    </row>
-    <row r="130" ht="14.5" customHeight="1" s="5">
-      <c r="A130" s="9" t="inlineStr">
+      <c r="G129" s="16" t="n"/>
+      <c r="H129" s="16" t="n"/>
+      <c r="I129" s="16" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="14" t="inlineStr">
         <is>
           <t>nova_iap_create_order_success</t>
         </is>
       </c>
-      <c r="B130" s="9" t="inlineStr">
+      <c r="B130" s="14" t="inlineStr">
         <is>
           <t>创建第三方订单成功</t>
         </is>
       </c>
-      <c r="C130" s="9" t="inlineStr">
-        <is>
-          <t>第三方支付订单创建成功。</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="C130" s="15" t="inlineStr">
+        <is>
+          <t>客户端订单、平台授权与支付 URL 已准备成功；此时尚未取得服务端订单号。</t>
+        </is>
+      </c>
+      <c r="D130" s="16" t="inlineStr">
         <is>
           <t>nova_table_id</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>商品配置表行 ID。</t>
-        </is>
-      </c>
-      <c r="G130" s="9" t="inlineStr">
+      <c r="E130" s="16" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F130" s="16" t="inlineStr">
+        <is>
+          <t>商品配置表行 ID；客户端使用 64 位整数。</t>
+        </is>
+      </c>
+      <c r="G130" s="16" t="inlineStr">
         <is>
           <t>第三方订单创建成功时上报。</t>
         </is>
       </c>
-      <c r="H130" s="9" t="inlineStr">
+      <c r="H130" s="16" t="inlineStr">
         <is>
           <t>tga</t>
         </is>
       </c>
-      <c r="I130" s="9" t="inlineStr">
+      <c r="I130" s="16" t="inlineStr">
         <is>
           <t>Mobile 官方内购不触发该事件。</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="14.5" customHeight="1" s="5">
+    <row r="131">
       <c r="A131" s="7" t="n"/>
       <c r="B131" s="7" t="n"/>
       <c r="C131" s="7" t="n"/>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="D131" s="16" t="inlineStr">
         <is>
           <t>nova_product_id</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="E131" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F131" s="16" t="inlineStr">
         <is>
           <t>平台侧商品 ID。</t>
         </is>
       </c>
-      <c r="G131" s="7" t="n"/>
-      <c r="H131" s="7" t="n"/>
-      <c r="I131" s="7" t="n"/>
-    </row>
-    <row r="132" ht="24" customHeight="1" s="5">
+      <c r="G131" s="16" t="n"/>
+      <c r="H131" s="16" t="n"/>
+      <c r="I131" s="16" t="n"/>
+    </row>
+    <row r="132">
       <c r="A132" s="7" t="n"/>
       <c r="B132" s="7" t="n"/>
       <c r="C132" s="7" t="n"/>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="D132" s="16" t="inlineStr">
         <is>
           <t>nova_debug</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E132" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>是否测试模式。</t>
-        </is>
-      </c>
-      <c r="G132" s="7" t="n"/>
-      <c r="H132" s="7" t="n"/>
-      <c r="I132" s="7" t="n"/>
-    </row>
-    <row r="133" ht="14.5" customHeight="1" s="5">
+      <c r="F132" s="16" t="inlineStr">
+        <is>
+          <t>是否 DevelopMode.Debug；不是 AlwaysPaySucceed。</t>
+        </is>
+      </c>
+      <c r="G132" s="16" t="n"/>
+      <c r="H132" s="16" t="n"/>
+      <c r="I132" s="16" t="n"/>
+    </row>
+    <row r="133">
       <c r="A133" s="7" t="n"/>
       <c r="B133" s="7" t="n"/>
       <c r="C133" s="7" t="n"/>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="D133" s="16" t="inlineStr">
         <is>
           <t>nova_price</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E133" s="16" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>商品本地化价格数值。</t>
-        </is>
-      </c>
-      <c r="G133" s="7" t="n"/>
-      <c r="H133" s="7" t="n"/>
-      <c r="I133" s="7" t="n"/>
-    </row>
-    <row r="134" ht="14.5" customHeight="1" s="5">
+      <c r="F133" s="16" t="inlineStr">
+        <is>
+          <t>支付表 Price 配置解析的价格数值；不是平台本地化价格或可信实付金额。</t>
+        </is>
+      </c>
+      <c r="G133" s="16" t="n"/>
+      <c r="H133" s="16" t="n"/>
+      <c r="I133" s="16" t="n"/>
+    </row>
+    <row r="134">
       <c r="A134" s="7" t="n"/>
       <c r="B134" s="7" t="n"/>
       <c r="C134" s="7" t="n"/>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="D134" s="16" t="inlineStr">
         <is>
           <t>nova_channel</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>支付渠道名称。</t>
-        </is>
-      </c>
-      <c r="G134" s="7" t="n"/>
-      <c r="H134" s="7" t="n"/>
-      <c r="I134" s="7" t="n"/>
-    </row>
-    <row r="135" ht="14.5" customFormat="1" customHeight="1" s="4">
+      <c r="E134" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F134" s="16" t="inlineStr">
+        <is>
+          <t>固定为 thirdpay。</t>
+        </is>
+      </c>
+      <c r="G134" s="16" t="n"/>
+      <c r="H134" s="16" t="n"/>
+      <c r="I134" s="16" t="n"/>
+    </row>
+    <row r="135">
       <c r="A135" s="7" t="n"/>
       <c r="B135" s="7" t="n"/>
       <c r="C135" s="7" t="n"/>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="D135" s="16" t="inlineStr">
         <is>
           <t>nova_client_order_id</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="E135" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F135" s="16" t="inlineStr">
         <is>
           <t>客户端生成的 ThirdPay 订单号。</t>
         </is>
       </c>
-      <c r="G135" s="7" t="n"/>
-      <c r="H135" s="7" t="n"/>
-      <c r="I135" s="7" t="n"/>
-    </row>
-    <row r="136" ht="14.5" customHeight="1" s="5">
+      <c r="G135" s="16" t="n"/>
+      <c r="H135" s="16" t="n"/>
+      <c r="I135" s="16" t="n"/>
+    </row>
+    <row r="136">
       <c r="A136" s="7" t="n"/>
       <c r="B136" s="7" t="n"/>
       <c r="C136" s="7" t="n"/>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D136" s="16" t="inlineStr">
         <is>
           <t>nova_server_order_id</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="E136" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F136" s="16" t="inlineStr">
         <is>
           <t>服务端确认的 ThirdPay 订单号；创建成功阶段尚未取得时为空。</t>
         </is>
       </c>
-      <c r="G136" s="7" t="n"/>
-      <c r="H136" s="7" t="n"/>
-      <c r="I136" s="7" t="n"/>
-    </row>
-    <row r="137" ht="14.5" customHeight="1" s="5">
+      <c r="G136" s="16" t="n"/>
+      <c r="H136" s="16" t="n"/>
+      <c r="I136" s="16" t="n"/>
+    </row>
+    <row r="137">
       <c r="A137" s="8" t="n"/>
       <c r="B137" s="8" t="n"/>
       <c r="C137" s="8" t="n"/>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="D137" s="16" t="inlineStr">
         <is>
           <t>nova_custom_data</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>业务层透传的自定义字符串参数。</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="n"/>
-      <c r="H137" s="8" t="n"/>
-      <c r="I137" s="8" t="n"/>
-    </row>
-    <row r="138" ht="14.5" customHeight="1" s="5">
-      <c r="A138" s="6" t="inlineStr">
+      <c r="E137" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F137" s="16" t="inlineStr">
+        <is>
+          <t>仅业务透传字符串非空时附带；框架不解析。</t>
+        </is>
+      </c>
+      <c r="G137" s="16" t="n"/>
+      <c r="H137" s="16" t="n"/>
+      <c r="I137" s="16" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="14" t="inlineStr">
         <is>
           <t>nova_iap_third_pay_close_order</t>
         </is>
       </c>
-      <c r="B138" s="6" t="inlineStr">
+      <c r="B138" s="14" t="inlineStr">
         <is>
           <t>关闭第三方收银台</t>
         </is>
       </c>
-      <c r="C138" s="6" t="inlineStr">
+      <c r="C138" s="15" t="inlineStr">
         <is>
           <t>支付会话已建立但未收到成功 pay_callback 的关闭、失败或异常终态。</t>
         </is>
       </c>
-      <c r="D138" s="3" t="inlineStr">
+      <c r="D138" s="16" t="inlineStr">
         <is>
           <t>nova_table_id</t>
         </is>
       </c>
-      <c r="E138" s="3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F138" s="3" t="inlineStr">
-        <is>
-          <t>商品配置表行 ID。</t>
-        </is>
-      </c>
-      <c r="G138" s="6" t="inlineStr">
+      <c r="E138" s="16" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F138" s="16" t="inlineStr">
+        <is>
+          <t>商品配置表行 ID；客户端使用 64 位整数。</t>
+        </is>
+      </c>
+      <c r="G138" s="16" t="inlineStr">
         <is>
           <t>仅作为支付页终态上报；与 nova_iap_local_pay_success 互斥。</t>
         </is>
       </c>
-      <c r="H138" s="6" t="inlineStr">
+      <c r="H138" s="16" t="inlineStr">
         <is>
           <t>tga</t>
         </is>
       </c>
-      <c r="I138" s="6" t="inlineStr">
+      <c r="I138" s="16" t="inlineStr">
         <is>
           <t>Mobile 官方内购不触发该事件。</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="14.5" customHeight="1" s="5">
+    <row r="139">
       <c r="A139" s="7" t="n"/>
       <c r="B139" s="7" t="n"/>
       <c r="C139" s="7" t="n"/>
-      <c r="D139" s="3" t="inlineStr">
+      <c r="D139" s="16" t="inlineStr">
         <is>
           <t>nova_product_id</t>
         </is>
       </c>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F139" s="3" t="inlineStr">
+      <c r="E139" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F139" s="16" t="inlineStr">
         <is>
           <t>平台侧商品 ID。</t>
         </is>
       </c>
-      <c r="G139" s="7" t="n"/>
-      <c r="H139" s="7" t="n"/>
-      <c r="I139" s="7" t="n"/>
-    </row>
-    <row r="140" ht="14.5" customHeight="1" s="5">
+      <c r="G139" s="16" t="n"/>
+      <c r="H139" s="16" t="n"/>
+      <c r="I139" s="16" t="n"/>
+    </row>
+    <row r="140">
       <c r="A140" s="7" t="n"/>
       <c r="B140" s="7" t="n"/>
       <c r="C140" s="7" t="n"/>
-      <c r="D140" s="3" t="inlineStr">
+      <c r="D140" s="16" t="inlineStr">
         <is>
           <t>nova_debug</t>
         </is>
       </c>
-      <c r="E140" s="3" t="inlineStr">
+      <c r="E140" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F140" s="3" t="inlineStr">
-        <is>
-          <t>是否测试模式。</t>
-        </is>
-      </c>
-      <c r="G140" s="7" t="n"/>
-      <c r="H140" s="7" t="n"/>
-      <c r="I140" s="7" t="n"/>
-    </row>
-    <row r="141" ht="14.5" customHeight="1" s="5">
+      <c r="F140" s="16" t="inlineStr">
+        <is>
+          <t>是否 DevelopMode.Debug；不是 AlwaysPaySucceed。</t>
+        </is>
+      </c>
+      <c r="G140" s="16" t="n"/>
+      <c r="H140" s="16" t="n"/>
+      <c r="I140" s="16" t="n"/>
+    </row>
+    <row r="141">
       <c r="A141" s="7" t="n"/>
       <c r="B141" s="7" t="n"/>
       <c r="C141" s="7" t="n"/>
-      <c r="D141" s="3" t="inlineStr">
+      <c r="D141" s="16" t="inlineStr">
         <is>
           <t>nova_price</t>
         </is>
       </c>
-      <c r="E141" s="3" t="inlineStr">
+      <c r="E141" s="16" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F141" s="3" t="inlineStr">
-        <is>
-          <t>商品本地化价格数值。</t>
-        </is>
-      </c>
-      <c r="G141" s="7" t="n"/>
-      <c r="H141" s="7" t="n"/>
-      <c r="I141" s="7" t="n"/>
-    </row>
-    <row r="142" ht="14.5" customHeight="1" s="5">
+      <c r="F141" s="16" t="inlineStr">
+        <is>
+          <t>支付表 Price 配置解析的价格数值；不是平台本地化价格或可信实付金额。</t>
+        </is>
+      </c>
+      <c r="G141" s="16" t="n"/>
+      <c r="H141" s="16" t="n"/>
+      <c r="I141" s="16" t="n"/>
+    </row>
+    <row r="142">
       <c r="A142" s="7" t="n"/>
       <c r="B142" s="7" t="n"/>
       <c r="C142" s="7" t="n"/>
-      <c r="D142" s="3" t="inlineStr">
+      <c r="D142" s="16" t="inlineStr">
         <is>
           <t>nova_channel</t>
         </is>
       </c>
-      <c r="E142" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F142" s="3" t="inlineStr">
-        <is>
-          <t>支付渠道名称。</t>
-        </is>
-      </c>
-      <c r="G142" s="7" t="n"/>
-      <c r="H142" s="7" t="n"/>
-      <c r="I142" s="7" t="n"/>
-    </row>
-    <row r="143" ht="14.5" customHeight="1" s="5">
+      <c r="E142" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F142" s="16" t="inlineStr">
+        <is>
+          <t>固定为 thirdpay。</t>
+        </is>
+      </c>
+      <c r="G142" s="16" t="n"/>
+      <c r="H142" s="16" t="n"/>
+      <c r="I142" s="16" t="n"/>
+    </row>
+    <row r="143">
       <c r="A143" s="7" t="n"/>
       <c r="B143" s="7" t="n"/>
       <c r="C143" s="7" t="n"/>
-      <c r="D143" s="3" t="inlineStr">
+      <c r="D143" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_type_id</t>
         </is>
       </c>
-      <c r="E143" s="3" t="inlineStr">
+      <c r="E143" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F143" s="3" t="inlineStr">
-        <is>
-          <t>第三方支付渠道 ID。</t>
-        </is>
-      </c>
-      <c r="G143" s="7" t="n"/>
-      <c r="H143" s="7" t="n"/>
-      <c r="I143" s="7" t="n"/>
-    </row>
-    <row r="144" ht="14.5" customHeight="1" s="5">
+      <c r="F143" s="16" t="inlineStr">
+        <is>
+          <t>当前客户端关闭支付页路径固定写入 0；不是已确认渠道 ID。</t>
+        </is>
+      </c>
+      <c r="G143" s="16" t="n"/>
+      <c r="H143" s="16" t="n"/>
+      <c r="I143" s="16" t="n"/>
+    </row>
+    <row r="144">
       <c r="A144" s="7" t="n"/>
       <c r="B144" s="7" t="n"/>
       <c r="C144" s="7" t="n"/>
-      <c r="D144" s="3" t="inlineStr">
+      <c r="D144" s="16" t="inlineStr">
         <is>
           <t>nova_custom_data</t>
         </is>
       </c>
-      <c r="E144" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F144" s="3" t="inlineStr">
-        <is>
-          <t>业务层透传的自定义字符串参数。</t>
-        </is>
-      </c>
-      <c r="G144" s="7" t="n"/>
-      <c r="H144" s="7" t="n"/>
-      <c r="I144" s="7" t="n"/>
-    </row>
-    <row r="145" ht="14.5" customHeight="1" s="5">
+      <c r="E144" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F144" s="16" t="inlineStr">
+        <is>
+          <t>仅业务透传字符串非空时附带；框架不解析。</t>
+        </is>
+      </c>
+      <c r="G144" s="16" t="n"/>
+      <c r="H144" s="16" t="n"/>
+      <c r="I144" s="16" t="n"/>
+    </row>
+    <row r="145">
       <c r="A145" s="7" t="n"/>
       <c r="B145" s="7" t="n"/>
       <c r="C145" s="7" t="n"/>
-      <c r="D145" s="3" t="inlineStr">
+      <c r="D145" s="16" t="inlineStr">
         <is>
           <t>nova_reason_detail</t>
         </is>
       </c>
-      <c r="E145" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F145" s="3" t="inlineStr">
+      <c r="E145" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F145" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 支付页关闭原因中文描述，与 nova_third_pay_close_reason 的枚举值一一对应。</t>
         </is>
       </c>
-      <c r="G145" s="7" t="n"/>
-      <c r="H145" s="7" t="n"/>
-      <c r="I145" s="7" t="n"/>
-    </row>
-    <row r="146" ht="14.5" customHeight="1" s="5">
+      <c r="G145" s="16" t="n"/>
+      <c r="H145" s="16" t="n"/>
+      <c r="I145" s="16" t="n"/>
+    </row>
+    <row r="146">
       <c r="A146" s="7" t="n"/>
       <c r="B146" s="7" t="n"/>
       <c r="C146" s="7" t="n"/>
-      <c r="D146" s="3" t="inlineStr">
+      <c r="D146" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_open_mode</t>
         </is>
       </c>
-      <c r="E146" s="3" t="inlineStr">
+      <c r="E146" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F146" s="3" t="inlineStr">
+      <c r="F146" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 支付页实际打开方式：0=打开失败，1=Auth Tab，2=Custom Tabs，3=系统浏览器回退，4=嵌入式 WebView，5=iOS Safe Browsing。</t>
         </is>
       </c>
-      <c r="G146" s="7" t="n"/>
-      <c r="H146" s="7" t="n"/>
-      <c r="I146" s="7" t="n"/>
-    </row>
-    <row r="147" ht="14.5" customHeight="1" s="5">
+      <c r="G146" s="16" t="n"/>
+      <c r="H146" s="16" t="n"/>
+      <c r="I146" s="16" t="n"/>
+    </row>
+    <row r="147">
       <c r="A147" s="7" t="n"/>
       <c r="B147" s="7" t="n"/>
       <c r="C147" s="7" t="n"/>
-      <c r="D147" s="3" t="inlineStr">
+      <c r="D147" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_callback_status</t>
         </is>
       </c>
-      <c r="E147" s="3" t="inlineStr">
+      <c r="E147" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F147" s="3" t="inlineStr">
+      <c r="F147" s="16" t="inlineStr">
         <is>
           <t>pay_callback 状态：0=未收到或无法识别，1=支付成功，2=支付失败，3=支付成功但渠道信息尚未同步。</t>
         </is>
       </c>
-      <c r="G147" s="7" t="n"/>
-      <c r="H147" s="7" t="n"/>
-      <c r="I147" s="7" t="n"/>
-    </row>
-    <row r="148" ht="14.5" customHeight="1" s="5">
+      <c r="G147" s="16" t="n"/>
+      <c r="H147" s="16" t="n"/>
+      <c r="I147" s="16" t="n"/>
+    </row>
+    <row r="148">
       <c r="A148" s="7" t="n"/>
       <c r="B148" s="7" t="n"/>
       <c r="C148" s="7" t="n"/>
-      <c r="D148" s="3" t="inlineStr">
+      <c r="D148" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_close_reason</t>
         </is>
       </c>
-      <c r="E148" s="3" t="inlineStr">
+      <c r="E148" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F148" s="3" t="inlineStr">
+      <c r="F148" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 关闭原因：0=未知，1=close_callback，2=嵌入式 WebView 关闭，3=iOS Safe Browsing 关闭，4=pay_callback 失败，5=未知 callback 状态，6=callback 参数无效，7=外部浏览器返回无成功 callback，8=callback 订单不匹配，9=验单开始后的迟到 callback，10=页面加载失败，11=Web 内容进程终止，12=页面异常，13=操作取消，14=会话被替换，15=Store 释放。</t>
         </is>
       </c>
-      <c r="G148" s="7" t="n"/>
-      <c r="H148" s="7" t="n"/>
-      <c r="I148" s="7" t="n"/>
-    </row>
-    <row r="149" ht="14.5" customHeight="1" s="5">
+      <c r="G148" s="16" t="n"/>
+      <c r="H148" s="16" t="n"/>
+      <c r="I148" s="16" t="n"/>
+    </row>
+    <row r="149">
       <c r="A149" s="7" t="n"/>
       <c r="B149" s="7" t="n"/>
       <c r="C149" s="7" t="n"/>
-      <c r="D149" s="3" t="inlineStr">
+      <c r="D149" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_failure_reason</t>
         </is>
       </c>
-      <c r="E149" s="3" t="inlineStr">
+      <c r="E149" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F149" s="3" t="inlineStr">
+      <c r="F149" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 支付/验单失败原因：0=未知，1=Store 禁用，2=Store 未初始化，3=重复支付，4=商品不存在，5=UID 缺失，6=支付配置不可用，7=服务端关闭支付，8=服务端未配置商品，9=WebView 服务不可用，10=外部浏览器服务不可用，11=Google 连接失败，12=Google token 创建失败，13=Google 支付 URL 构建失败，14=Google 用户取消，15=支付页打开失败，16=支付页打开异常，17=系统浏览器回退 URL 为空，18=callback 支付失败，19=callback 参数无效，20=callback 状态未知，21=callback 订单不匹配，22=callback 到达时已开始验单，23=外部浏览器返回无成功 callback，24=验单服务不可用，25=验单网络失败，26=验单响应缺少订单，27=服务端待支付，28=服务端处理中，29=服务端失败或过期，30=服务端订单不存在，31=未知服务端订单状态，32=操作取消，33=会话被替换，34=Store 释放，35=未分类异常，36=第三方支付 URL 构建失败，37=授权完成但支付 URL 缺失。</t>
         </is>
       </c>
-      <c r="G149" s="7" t="n"/>
-      <c r="H149" s="7" t="n"/>
-      <c r="I149" s="7" t="n"/>
-    </row>
-    <row r="150" ht="14.5" customHeight="1" s="5">
+      <c r="G149" s="16" t="n"/>
+      <c r="H149" s="16" t="n"/>
+      <c r="I149" s="16" t="n"/>
+    </row>
+    <row r="150">
       <c r="A150" s="7" t="n"/>
       <c r="B150" s="7" t="n"/>
       <c r="C150" s="7" t="n"/>
-      <c r="D150" s="3" t="inlineStr">
+      <c r="D150" s="16" t="inlineStr">
         <is>
           <t>nova_client_order_id</t>
         </is>
       </c>
-      <c r="E150" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F150" s="3" t="inlineStr">
+      <c r="E150" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F150" s="16" t="inlineStr">
         <is>
           <t>客户端生成的 ThirdPay 订单号。</t>
         </is>
       </c>
-      <c r="G150" s="7" t="n"/>
-      <c r="H150" s="7" t="n"/>
-      <c r="I150" s="7" t="n"/>
+      <c r="G150" s="16" t="n"/>
+      <c r="H150" s="16" t="n"/>
+      <c r="I150" s="16" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="7" t="n"/>
       <c r="B151" s="7" t="n"/>
       <c r="C151" s="7" t="n"/>
-      <c r="D151" s="3" t="inlineStr">
+      <c r="D151" s="16" t="inlineStr">
         <is>
           <t>nova_server_order_id</t>
         </is>
       </c>
-      <c r="E151" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F151" s="3" t="inlineStr">
+      <c r="E151" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F151" s="16" t="inlineStr">
         <is>
           <t>服务端确认的 ThirdPay 订单号；无返回时为空。</t>
         </is>
       </c>
-      <c r="G151" s="7" t="n"/>
-      <c r="H151" s="7" t="n"/>
-      <c r="I151" s="7" t="n"/>
+      <c r="G151" s="16" t="n"/>
+      <c r="H151" s="16" t="n"/>
+      <c r="I151" s="16" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="7" t="n"/>
       <c r="B152" s="7" t="n"/>
       <c r="C152" s="7" t="n"/>
-      <c r="D152" s="3" t="inlineStr">
+      <c r="D152" s="16" t="inlineStr">
         <is>
           <t>nova_native_error_code</t>
         </is>
       </c>
-      <c r="E152" s="3" t="inlineStr">
+      <c r="E152" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F152" s="3" t="inlineStr">
+      <c r="F152" s="16" t="inlineStr">
         <is>
           <t>支付页或原生能力返回的错误码；无错误时为 0。</t>
         </is>
       </c>
-      <c r="G152" s="7" t="n"/>
-      <c r="H152" s="7" t="n"/>
-      <c r="I152" s="7" t="n"/>
+      <c r="G152" s="16" t="n"/>
+      <c r="H152" s="16" t="n"/>
+      <c r="I152" s="16" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="8" t="n"/>
       <c r="B153" s="8" t="n"/>
       <c r="C153" s="8" t="n"/>
-      <c r="D153" s="3" t="inlineStr">
+      <c r="D153" s="16" t="inlineStr">
         <is>
           <t>nova_native_error_message</t>
         </is>
       </c>
-      <c r="E153" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F153" s="3" t="inlineStr">
+      <c r="E153" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F153" s="16" t="inlineStr">
         <is>
           <t>支付页或原生能力返回的错误描述。</t>
         </is>
       </c>
-      <c r="G153" s="8" t="n"/>
-      <c r="H153" s="8" t="n"/>
-      <c r="I153" s="8" t="n"/>
+      <c r="G153" s="16" t="n"/>
+      <c r="H153" s="16" t="n"/>
+      <c r="I153" s="16" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="9" t="inlineStr">
+      <c r="A154" s="14" t="inlineStr">
         <is>
           <t>pay_success</t>
         </is>
       </c>
-      <c r="B154" s="9" t="inlineStr">
+      <c r="B154" s="14" t="inlineStr">
         <is>
           <t>支付成功(移动支付+第三方支付)</t>
         </is>
       </c>
-      <c r="C154" s="9" t="inlineStr">
+      <c r="C154" s="15" t="inlineStr">
         <is>
           <t>客户端支付成功后找服务器订单验证后的打点（服务器打点）</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="D154" s="16" t="inlineStr">
         <is>
           <t>nova_debug</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E154" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F154" s="16" t="inlineStr">
         <is>
           <t>是否是测试订单</t>
         </is>
       </c>
-      <c r="G154" s="9" t="inlineStr">
+      <c r="G154" s="16" t="inlineStr">
         <is>
           <t>服务器确认支付成功时上报。</t>
         </is>
       </c>
-      <c r="H154" s="9" t="inlineStr">
+      <c r="H154" s="16" t="inlineStr">
         <is>
           <t>tga</t>
         </is>
       </c>
-      <c r="I154" s="9" t="inlineStr">
-        <is>
-          <t>服务器打点。事件名为 TGA 固有命名。</t>
+      <c r="I154" s="16" t="inlineStr">
+        <is>
+          <t>服务器打点。事件名为 TGA 固有命名。 本表登记服务端约定；当前客户端源码不发起，尚未核验已部署服务端。</t>
         </is>
       </c>
     </row>
@@ -4442,301 +4487,301 @@
       <c r="A155" s="7" t="n"/>
       <c r="B155" s="7" t="n"/>
       <c r="C155" s="7" t="n"/>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="D155" s="16" t="inlineStr">
         <is>
           <t>nova_table_id</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E155" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F155" s="16" t="inlineStr">
         <is>
           <t>purchase表格中的id</t>
         </is>
       </c>
-      <c r="G155" s="7" t="n"/>
-      <c r="H155" s="7" t="n"/>
-      <c r="I155" s="7" t="n"/>
+      <c r="G155" s="16" t="n"/>
+      <c r="H155" s="16" t="n"/>
+      <c r="I155" s="16" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="7" t="n"/>
       <c r="B156" s="7" t="n"/>
       <c r="C156" s="7" t="n"/>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="D156" s="16" t="inlineStr">
         <is>
           <t>nova_price</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E156" s="16" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F156" s="16" t="inlineStr">
         <is>
           <t>purchase表格中price字段的值</t>
         </is>
       </c>
-      <c r="G156" s="7" t="n"/>
-      <c r="H156" s="7" t="n"/>
-      <c r="I156" s="7" t="n"/>
+      <c r="G156" s="16" t="n"/>
+      <c r="H156" s="16" t="n"/>
+      <c r="I156" s="16" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="7" t="n"/>
       <c r="B157" s="7" t="n"/>
       <c r="C157" s="7" t="n"/>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="D157" s="16" t="inlineStr">
         <is>
           <t>nova_channel</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E157" s="16" t="inlineStr">
         <is>
           <t>enum-string</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F157" s="16" t="inlineStr">
         <is>
           <t>ios 商店</t>
         </is>
       </c>
-      <c r="G157" s="7" t="n"/>
-      <c r="H157" s="7" t="n"/>
-      <c r="I157" s="7" t="n"/>
+      <c r="G157" s="16" t="n"/>
+      <c r="H157" s="16" t="n"/>
+      <c r="I157" s="16" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="7" t="n"/>
       <c r="B158" s="7" t="n"/>
       <c r="C158" s="7" t="n"/>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="D158" s="16" t="inlineStr">
         <is>
           <t>nova_order_id</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="E158" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F158" s="16" t="inlineStr">
         <is>
           <t>订单id</t>
         </is>
       </c>
-      <c r="G158" s="7" t="n"/>
-      <c r="H158" s="7" t="n"/>
-      <c r="I158" s="7" t="n"/>
+      <c r="G158" s="16" t="n"/>
+      <c r="H158" s="16" t="n"/>
+      <c r="I158" s="16" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="7" t="n"/>
       <c r="B159" s="7" t="n"/>
       <c r="C159" s="7" t="n"/>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="D159" s="16" t="inlineStr">
         <is>
           <t>nova_uid</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E159" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F159" s="16" t="inlineStr">
         <is>
           <t>游戏用户唯一标识</t>
         </is>
       </c>
-      <c r="G159" s="7" t="n"/>
-      <c r="H159" s="7" t="n"/>
-      <c r="I159" s="7" t="n"/>
-    </row>
-    <row r="160" ht="29" customHeight="1" s="5">
+      <c r="G159" s="16" t="n"/>
+      <c r="H159" s="16" t="n"/>
+      <c r="I159" s="16" t="n"/>
+    </row>
+    <row r="160">
       <c r="A160" s="7" t="n"/>
       <c r="B160" s="7" t="n"/>
       <c r="C160" s="7" t="n"/>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="D160" s="16" t="inlineStr">
         <is>
           <t>nova_device_id</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="E160" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F160" s="16" t="inlineStr">
         <is>
           <t>设备id</t>
         </is>
       </c>
-      <c r="G160" s="7" t="n"/>
-      <c r="H160" s="7" t="n"/>
-      <c r="I160" s="7" t="n"/>
-    </row>
-    <row r="161" ht="29" customHeight="1" s="5">
+      <c r="G160" s="16" t="n"/>
+      <c r="H160" s="16" t="n"/>
+      <c r="I160" s="16" t="n"/>
+    </row>
+    <row r="161">
       <c r="A161" s="7" t="n"/>
       <c r="B161" s="7" t="n"/>
       <c r="C161" s="7" t="n"/>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="D161" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_type_id</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E161" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F161" s="16" t="inlineStr">
         <is>
           <t>第三方支付渠道ID
 (仅第三方支付时有值)</t>
         </is>
       </c>
-      <c r="G161" s="7" t="n"/>
-      <c r="H161" s="7" t="n"/>
-      <c r="I161" s="7" t="n"/>
+      <c r="G161" s="16" t="n"/>
+      <c r="H161" s="16" t="n"/>
+      <c r="I161" s="16" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="n"/>
       <c r="B162" s="7" t="n"/>
       <c r="C162" s="7" t="n"/>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="D162" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_method</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="E162" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F162" s="16" t="inlineStr">
         <is>
           <t>第三方支付渠道名字
 (仅第三方支付时有值)</t>
         </is>
       </c>
-      <c r="G162" s="7" t="n"/>
-      <c r="H162" s="7" t="n"/>
-      <c r="I162" s="7" t="n"/>
+      <c r="G162" s="16" t="n"/>
+      <c r="H162" s="16" t="n"/>
+      <c r="I162" s="16" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="7" t="n"/>
       <c r="B163" s="7" t="n"/>
       <c r="C163" s="7" t="n"/>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="D163" s="16" t="inlineStr">
         <is>
           <t>nova_product_id</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="G163" s="7" t="n"/>
-      <c r="H163" s="7" t="n"/>
-      <c r="I163" s="7" t="n"/>
-    </row>
-    <row r="164" ht="29" customHeight="1" s="5">
+      <c r="E163" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F163" s="16" t="inlineStr">
+        <is>
+          <t>平台商品 ID / SKU（既有服务端约定，需由服务端核验实际值）。</t>
+        </is>
+      </c>
+      <c r="G163" s="16" t="n"/>
+      <c r="H163" s="16" t="n"/>
+      <c r="I163" s="16" t="n"/>
+    </row>
+    <row r="164">
       <c r="A164" s="7" t="n"/>
       <c r="B164" s="7" t="n"/>
       <c r="C164" s="7" t="n"/>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="D164" s="16" t="inlineStr">
         <is>
           <t>nova_google_verify_permission_denied</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E164" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>服务器订单校验权限不足，默认false, 谷歌返回403时为true</t>
-        </is>
-      </c>
-      <c r="G164" s="7" t="n"/>
-      <c r="H164" s="7" t="n"/>
-      <c r="I164" s="7" t="n"/>
+      <c r="F164" s="16" t="inlineStr">
+        <is>
+          <t>既有服务端约定：Google 验单返回 403 权限不足时为 true；部署行为待服务端核验。</t>
+        </is>
+      </c>
+      <c r="G164" s="16" t="n"/>
+      <c r="H164" s="16" t="n"/>
+      <c r="I164" s="16" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="8" t="n"/>
       <c r="B165" s="8" t="n"/>
       <c r="C165" s="8" t="n"/>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="D165" s="16" t="inlineStr">
         <is>
           <t>nova_server_validate_transaction_local</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E165" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>服务器本次订单校验是否是通过本地数据库获取数据,true:是，false:去谷歌或者苹果服务器教研</t>
-        </is>
-      </c>
-      <c r="G165" s="8" t="n"/>
-      <c r="H165" s="8" t="n"/>
-      <c r="I165" s="8" t="n"/>
+      <c r="F165" s="16" t="inlineStr">
+        <is>
+          <t>既有服务端约定：true 表示本次从本地数据库取得校验数据；false 表示访问 Google 或 Apple 验单服务。</t>
+        </is>
+      </c>
+      <c r="G165" s="16" t="n"/>
+      <c r="H165" s="16" t="n"/>
+      <c r="I165" s="16" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="6" t="inlineStr">
+      <c r="A166" s="14" t="inlineStr">
         <is>
           <t>af_purchase</t>
         </is>
       </c>
-      <c r="B166" s="6" t="inlineStr">
+      <c r="B166" s="14" t="inlineStr">
         <is>
           <t>支付成功(移动支付+第三方支付)</t>
         </is>
       </c>
-      <c r="C166" s="6" t="inlineStr">
+      <c r="C166" s="15" t="inlineStr">
         <is>
           <t>客户端支付成功后找服务器订单验证后的打点（服务器打点）</t>
         </is>
       </c>
-      <c r="D166" s="3" t="inlineStr">
+      <c r="D166" s="16" t="inlineStr">
         <is>
           <t>af_order_id</t>
         </is>
       </c>
-      <c r="E166" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F166" s="3" t="inlineStr">
+      <c r="E166" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F166" s="16" t="inlineStr">
         <is>
           <t>订单id</t>
         </is>
       </c>
-      <c r="G166" s="6" t="inlineStr">
+      <c r="G166" s="16" t="inlineStr">
         <is>
           <t>服务器确认支付成功时上报。</t>
         </is>
       </c>
-      <c r="H166" s="6" t="inlineStr">
+      <c r="H166" s="16" t="inlineStr">
         <is>
           <t>appsflyer</t>
         </is>
       </c>
-      <c r="I166" s="6" t="inlineStr">
-        <is>
-          <t>服务器打点。</t>
+      <c r="I166" s="16" t="inlineStr">
+        <is>
+          <t>服务器打点。 本表登记服务端约定；当前客户端源码不发起，尚未核验已部署服务端。</t>
         </is>
       </c>
     </row>
@@ -4744,412 +4789,417 @@
       <c r="A167" s="7" t="n"/>
       <c r="B167" s="7" t="n"/>
       <c r="C167" s="7" t="n"/>
-      <c r="D167" s="3" t="inlineStr">
+      <c r="D167" s="16" t="inlineStr">
         <is>
           <t>af_content_id</t>
         </is>
       </c>
-      <c r="E167" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F167" s="3" t="inlineStr">
+      <c r="E167" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F167" s="16" t="inlineStr">
         <is>
           <t>订单sku</t>
         </is>
       </c>
-      <c r="G167" s="7" t="n"/>
-      <c r="H167" s="7" t="n"/>
-      <c r="I167" s="7" t="n"/>
+      <c r="G167" s="16" t="n"/>
+      <c r="H167" s="16" t="n"/>
+      <c r="I167" s="16" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="7" t="n"/>
       <c r="B168" s="7" t="n"/>
       <c r="C168" s="7" t="n"/>
-      <c r="D168" s="3" t="inlineStr">
+      <c r="D168" s="16" t="inlineStr">
         <is>
           <t>af_baseplan_id</t>
         </is>
       </c>
-      <c r="E168" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F168" s="3" t="inlineStr">
+      <c r="E168" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F168" s="16" t="inlineStr">
         <is>
           <t>订单sku</t>
         </is>
       </c>
-      <c r="G168" s="7" t="n"/>
-      <c r="H168" s="7" t="n"/>
-      <c r="I168" s="7" t="n"/>
+      <c r="G168" s="16" t="n"/>
+      <c r="H168" s="16" t="n"/>
+      <c r="I168" s="16" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="7" t="n"/>
       <c r="B169" s="7" t="n"/>
       <c r="C169" s="7" t="n"/>
-      <c r="D169" s="3" t="inlineStr">
+      <c r="D169" s="16" t="inlineStr">
         <is>
           <t>af_currency</t>
         </is>
       </c>
-      <c r="E169" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F169" s="3" t="inlineStr">
+      <c r="E169" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F169" s="16" t="inlineStr">
         <is>
           <t>货币单位</t>
         </is>
       </c>
-      <c r="G169" s="7" t="n"/>
-      <c r="H169" s="7" t="n"/>
-      <c r="I169" s="7" t="n"/>
+      <c r="G169" s="16" t="n"/>
+      <c r="H169" s="16" t="n"/>
+      <c r="I169" s="16" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="7" t="n"/>
       <c r="B170" s="7" t="n"/>
       <c r="C170" s="7" t="n"/>
-      <c r="D170" s="3" t="inlineStr">
+      <c r="D170" s="16" t="inlineStr">
         <is>
           <t>af_quantity</t>
         </is>
       </c>
-      <c r="E170" s="3" t="inlineStr">
+      <c r="E170" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F170" s="3" t="inlineStr">
+      <c r="F170" s="16" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="G170" s="7" t="n"/>
-      <c r="H170" s="7" t="n"/>
-      <c r="I170" s="7" t="n"/>
+      <c r="G170" s="16" t="n"/>
+      <c r="H170" s="16" t="n"/>
+      <c r="I170" s="16" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="7" t="n"/>
       <c r="B171" s="7" t="n"/>
       <c r="C171" s="7" t="n"/>
-      <c r="D171" s="3" t="inlineStr">
+      <c r="D171" s="16" t="inlineStr">
         <is>
           <t>af_validated</t>
         </is>
       </c>
-      <c r="E171" s="3" t="inlineStr">
+      <c r="E171" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F171" s="3" t="inlineStr">
+      <c r="F171" s="16" t="inlineStr">
         <is>
           <t>是否校验成功</t>
         </is>
       </c>
-      <c r="G171" s="7" t="n"/>
-      <c r="H171" s="7" t="n"/>
-      <c r="I171" s="7" t="n"/>
+      <c r="G171" s="16" t="n"/>
+      <c r="H171" s="16" t="n"/>
+      <c r="I171" s="16" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="7" t="n"/>
       <c r="B172" s="7" t="n"/>
       <c r="C172" s="7" t="n"/>
-      <c r="D172" s="3" t="inlineStr">
+      <c r="D172" s="16" t="inlineStr">
         <is>
           <t>af_revenue</t>
         </is>
       </c>
-      <c r="E172" s="3" t="inlineStr">
+      <c r="E172" s="16" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F172" s="3" t="inlineStr">
+      <c r="F172" s="16" t="inlineStr">
         <is>
           <t>价格</t>
         </is>
       </c>
-      <c r="G172" s="7" t="n"/>
-      <c r="H172" s="7" t="n"/>
-      <c r="I172" s="7" t="n"/>
+      <c r="G172" s="16" t="n"/>
+      <c r="H172" s="16" t="n"/>
+      <c r="I172" s="16" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="7" t="n"/>
       <c r="B173" s="7" t="n"/>
       <c r="C173" s="7" t="n"/>
-      <c r="D173" s="3" t="inlineStr">
+      <c r="D173" s="16" t="inlineStr">
         <is>
           <t>nova_google_verify_permission_denied</t>
         </is>
       </c>
-      <c r="E173" s="3" t="inlineStr">
+      <c r="E173" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="G173" s="7" t="n"/>
-      <c r="H173" s="7" t="n"/>
-      <c r="I173" s="7" t="n"/>
+      <c r="F173" s="16" t="inlineStr">
+        <is>
+          <t>既有服务端约定：Google 验单返回 403 权限不足时为 true；部署行为待服务端核验。</t>
+        </is>
+      </c>
+      <c r="G173" s="16" t="n"/>
+      <c r="H173" s="16" t="n"/>
+      <c r="I173" s="16" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="7" t="n"/>
       <c r="B174" s="7" t="n"/>
       <c r="C174" s="7" t="n"/>
-      <c r="D174" s="3" t="inlineStr">
+      <c r="D174" s="16" t="inlineStr">
         <is>
           <t>nova_debug</t>
         </is>
       </c>
-      <c r="E174" s="3" t="inlineStr">
+      <c r="E174" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F174" s="3" t="inlineStr">
+      <c r="F174" s="16" t="inlineStr">
         <is>
           <t>是否是测试订单</t>
         </is>
       </c>
-      <c r="G174" s="7" t="n"/>
-      <c r="H174" s="7" t="n"/>
-      <c r="I174" s="7" t="n"/>
+      <c r="G174" s="16" t="n"/>
+      <c r="H174" s="16" t="n"/>
+      <c r="I174" s="16" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="7" t="n"/>
       <c r="B175" s="7" t="n"/>
       <c r="C175" s="7" t="n"/>
-      <c r="D175" s="3" t="inlineStr">
+      <c r="D175" s="16" t="inlineStr">
         <is>
           <t>nova_table_id</t>
         </is>
       </c>
-      <c r="E175" s="3" t="inlineStr">
+      <c r="E175" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F175" s="3" t="inlineStr">
+      <c r="F175" s="16" t="inlineStr">
         <is>
           <t>purchase表格中的id</t>
         </is>
       </c>
-      <c r="G175" s="7" t="n"/>
-      <c r="H175" s="7" t="n"/>
-      <c r="I175" s="7" t="n"/>
+      <c r="G175" s="16" t="n"/>
+      <c r="H175" s="16" t="n"/>
+      <c r="I175" s="16" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="7" t="n"/>
       <c r="B176" s="7" t="n"/>
       <c r="C176" s="7" t="n"/>
-      <c r="D176" s="3" t="inlineStr">
+      <c r="D176" s="16" t="inlineStr">
         <is>
           <t>nova_price</t>
         </is>
       </c>
-      <c r="E176" s="3" t="inlineStr">
+      <c r="E176" s="16" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F176" s="3" t="inlineStr">
+      <c r="F176" s="16" t="inlineStr">
         <is>
           <t>purchase表格中price字段的值</t>
         </is>
       </c>
-      <c r="G176" s="7" t="n"/>
-      <c r="H176" s="7" t="n"/>
-      <c r="I176" s="7" t="n"/>
+      <c r="G176" s="16" t="n"/>
+      <c r="H176" s="16" t="n"/>
+      <c r="I176" s="16" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="7" t="n"/>
       <c r="B177" s="7" t="n"/>
       <c r="C177" s="7" t="n"/>
-      <c r="D177" s="3" t="inlineStr">
+      <c r="D177" s="16" t="inlineStr">
         <is>
           <t>nova_channel</t>
         </is>
       </c>
-      <c r="E177" s="3" t="inlineStr">
+      <c r="E177" s="16" t="inlineStr">
         <is>
           <t>enum-string</t>
         </is>
       </c>
-      <c r="F177" s="3" t="inlineStr">
+      <c r="F177" s="16" t="inlineStr">
         <is>
           <t>ios 商店</t>
         </is>
       </c>
-      <c r="G177" s="7" t="n"/>
-      <c r="H177" s="7" t="n"/>
-      <c r="I177" s="7" t="n"/>
-    </row>
-    <row r="178" ht="29" customHeight="1" s="5">
+      <c r="G177" s="16" t="n"/>
+      <c r="H177" s="16" t="n"/>
+      <c r="I177" s="16" t="n"/>
+    </row>
+    <row r="178">
       <c r="A178" s="7" t="n"/>
       <c r="B178" s="7" t="n"/>
       <c r="C178" s="7" t="n"/>
-      <c r="D178" s="3" t="inlineStr">
+      <c r="D178" s="16" t="inlineStr">
         <is>
           <t>nova_order_id</t>
         </is>
       </c>
-      <c r="E178" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F178" s="3" t="inlineStr">
+      <c r="E178" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F178" s="16" t="inlineStr">
         <is>
           <t>订单id</t>
         </is>
       </c>
-      <c r="G178" s="7" t="n"/>
-      <c r="H178" s="7" t="n"/>
-      <c r="I178" s="7" t="n"/>
-    </row>
-    <row r="179" ht="29" customHeight="1" s="5">
+      <c r="G178" s="16" t="n"/>
+      <c r="H178" s="16" t="n"/>
+      <c r="I178" s="16" t="n"/>
+    </row>
+    <row r="179">
       <c r="A179" s="7" t="n"/>
       <c r="B179" s="7" t="n"/>
       <c r="C179" s="7" t="n"/>
-      <c r="D179" s="3" t="inlineStr">
+      <c r="D179" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_type_id</t>
         </is>
       </c>
-      <c r="E179" s="3" t="inlineStr">
+      <c r="E179" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F179" s="3" t="inlineStr">
+      <c r="F179" s="16" t="inlineStr">
         <is>
           <t>第三方支付渠道ID
 (仅第三方支付时有值)</t>
         </is>
       </c>
-      <c r="G179" s="7" t="n"/>
-      <c r="H179" s="7" t="n"/>
-      <c r="I179" s="7" t="n"/>
+      <c r="G179" s="16" t="n"/>
+      <c r="H179" s="16" t="n"/>
+      <c r="I179" s="16" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="7" t="n"/>
       <c r="B180" s="7" t="n"/>
       <c r="C180" s="7" t="n"/>
-      <c r="D180" s="3" t="inlineStr">
+      <c r="D180" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_method</t>
         </is>
       </c>
-      <c r="E180" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F180" s="3" t="inlineStr">
+      <c r="E180" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F180" s="16" t="inlineStr">
         <is>
           <t>第三方支付渠道名字
 (仅第三方支付时有值)</t>
         </is>
       </c>
-      <c r="G180" s="7" t="n"/>
-      <c r="H180" s="7" t="n"/>
-      <c r="I180" s="7" t="n"/>
+      <c r="G180" s="16" t="n"/>
+      <c r="H180" s="16" t="n"/>
+      <c r="I180" s="16" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="7" t="n"/>
       <c r="B181" s="7" t="n"/>
       <c r="C181" s="7" t="n"/>
-      <c r="D181" s="3" t="inlineStr">
+      <c r="D181" s="16" t="inlineStr">
         <is>
           <t>nova_product_id</t>
         </is>
       </c>
-      <c r="E181" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F181" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="G181" s="7" t="n"/>
-      <c r="H181" s="7" t="n"/>
-      <c r="I181" s="7" t="n"/>
+      <c r="E181" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F181" s="16" t="inlineStr">
+        <is>
+          <t>平台商品 ID / SKU（既有服务端约定，需由服务端核验实际值）。</t>
+        </is>
+      </c>
+      <c r="G181" s="16" t="n"/>
+      <c r="H181" s="16" t="n"/>
+      <c r="I181" s="16" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="8" t="n"/>
       <c r="B182" s="8" t="n"/>
       <c r="C182" s="8" t="n"/>
-      <c r="D182" s="3" t="inlineStr">
+      <c r="D182" s="16" t="inlineStr">
         <is>
           <t>nova_uid</t>
         </is>
       </c>
-      <c r="E182" s="3" t="inlineStr">
+      <c r="E182" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F182" s="3" t="inlineStr">
+      <c r="F182" s="16" t="inlineStr">
         <is>
           <t>游戏用户唯一标识</t>
         </is>
       </c>
-      <c r="G182" s="8" t="n"/>
-      <c r="H182" s="8" t="n"/>
-      <c r="I182" s="8" t="n"/>
+      <c r="G182" s="16" t="n"/>
+      <c r="H182" s="16" t="n"/>
+      <c r="I182" s="16" t="n"/>
     </row>
     <row r="183">
-      <c r="A183" s="9" t="inlineStr">
+      <c r="A183" s="14" t="inlineStr">
         <is>
           <t>af_purchase_sandbox_s2s</t>
         </is>
       </c>
-      <c r="B183" s="9" t="inlineStr">
+      <c r="B183" s="14" t="inlineStr">
         <is>
           <t>支付成功(移动支付+第三方支付)</t>
         </is>
       </c>
-      <c r="C183" s="9" t="inlineStr">
+      <c r="C183" s="15" t="inlineStr">
         <is>
           <t>客户端支付成功后找服务器订单验证后的打点（服务器打点）
 （谷歌的测试账号,ios的沙箱账号）购买</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D183" s="16" t="inlineStr">
         <is>
           <t>af_order_id</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="E183" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F183" s="16" t="inlineStr">
         <is>
           <t>订单id</t>
         </is>
       </c>
-      <c r="G183" s="9" t="inlineStr">
+      <c r="G183" s="16" t="inlineStr">
         <is>
           <t>服务器确认支付成功时上报。</t>
         </is>
       </c>
-      <c r="H183" s="9" t="inlineStr">
+      <c r="H183" s="16" t="inlineStr">
         <is>
           <t>appsflyer</t>
         </is>
       </c>
-      <c r="I183" s="9" t="inlineStr">
-        <is>
-          <t>服务器打点。</t>
+      <c r="I183" s="16" t="inlineStr">
+        <is>
+          <t>服务器打点。 本表登记服务端约定；当前客户端源码不发起，尚未核验已部署服务端。</t>
         </is>
       </c>
     </row>
@@ -5157,901 +5207,859 @@
       <c r="A184" s="7" t="n"/>
       <c r="B184" s="7" t="n"/>
       <c r="C184" s="7" t="n"/>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D184" s="16" t="inlineStr">
         <is>
           <t>af_content_id</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="E184" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F184" s="16" t="inlineStr">
         <is>
           <t>订单sku</t>
         </is>
       </c>
-      <c r="G184" s="7" t="n"/>
-      <c r="H184" s="7" t="n"/>
-      <c r="I184" s="7" t="n"/>
+      <c r="G184" s="16" t="n"/>
+      <c r="H184" s="16" t="n"/>
+      <c r="I184" s="16" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="7" t="n"/>
       <c r="B185" s="7" t="n"/>
       <c r="C185" s="7" t="n"/>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D185" s="16" t="inlineStr">
         <is>
           <t>af_baseplan_id</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="E185" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F185" s="16" t="inlineStr">
         <is>
           <t>订单sku</t>
         </is>
       </c>
-      <c r="G185" s="7" t="n"/>
-      <c r="H185" s="7" t="n"/>
-      <c r="I185" s="7" t="n"/>
+      <c r="G185" s="16" t="n"/>
+      <c r="H185" s="16" t="n"/>
+      <c r="I185" s="16" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="7" t="n"/>
       <c r="B186" s="7" t="n"/>
       <c r="C186" s="7" t="n"/>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D186" s="16" t="inlineStr">
         <is>
           <t>af_currency</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="E186" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F186" s="16" t="inlineStr">
         <is>
           <t>货币单位</t>
         </is>
       </c>
-      <c r="G186" s="7" t="n"/>
-      <c r="H186" s="7" t="n"/>
-      <c r="I186" s="7" t="n"/>
+      <c r="G186" s="16" t="n"/>
+      <c r="H186" s="16" t="n"/>
+      <c r="I186" s="16" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="7" t="n"/>
       <c r="B187" s="7" t="n"/>
       <c r="C187" s="7" t="n"/>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="D187" s="16" t="inlineStr">
         <is>
           <t>af_quantity</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E187" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F187" s="16" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="G187" s="7" t="n"/>
-      <c r="H187" s="7" t="n"/>
-      <c r="I187" s="7" t="n"/>
+      <c r="G187" s="16" t="n"/>
+      <c r="H187" s="16" t="n"/>
+      <c r="I187" s="16" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="7" t="n"/>
       <c r="B188" s="7" t="n"/>
       <c r="C188" s="7" t="n"/>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="D188" s="16" t="inlineStr">
         <is>
           <t>af_validated</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E188" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F188" s="16" t="inlineStr">
         <is>
           <t>是否校验成功</t>
         </is>
       </c>
-      <c r="G188" s="7" t="n"/>
-      <c r="H188" s="7" t="n"/>
-      <c r="I188" s="7" t="n"/>
+      <c r="G188" s="16" t="n"/>
+      <c r="H188" s="16" t="n"/>
+      <c r="I188" s="16" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="7" t="n"/>
       <c r="B189" s="7" t="n"/>
       <c r="C189" s="7" t="n"/>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="D189" s="16" t="inlineStr">
         <is>
           <t>af_revenue_test</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E189" s="16" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F189" s="16" t="inlineStr">
         <is>
           <t>价格</t>
         </is>
       </c>
-      <c r="G189" s="7" t="n"/>
-      <c r="H189" s="7" t="n"/>
-      <c r="I189" s="7" t="n"/>
+      <c r="G189" s="16" t="n"/>
+      <c r="H189" s="16" t="n"/>
+      <c r="I189" s="16" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="7" t="n"/>
       <c r="B190" s="7" t="n"/>
       <c r="C190" s="7" t="n"/>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D190" s="16" t="inlineStr">
         <is>
           <t>nova_google_verify_permission_denied</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E190" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="G190" s="7" t="n"/>
-      <c r="H190" s="7" t="n"/>
-      <c r="I190" s="7" t="n"/>
+      <c r="F190" s="16" t="inlineStr">
+        <is>
+          <t>既有服务端约定：Google 验单返回 403 权限不足时为 true；部署行为待服务端核验。</t>
+        </is>
+      </c>
+      <c r="G190" s="16" t="n"/>
+      <c r="H190" s="16" t="n"/>
+      <c r="I190" s="16" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="7" t="n"/>
       <c r="B191" s="7" t="n"/>
       <c r="C191" s="7" t="n"/>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D191" s="16" t="inlineStr">
         <is>
           <t>nova_debug</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E191" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F191" s="16" t="inlineStr">
         <is>
           <t>是否是测试订单</t>
         </is>
       </c>
-      <c r="G191" s="7" t="n"/>
-      <c r="H191" s="7" t="n"/>
-      <c r="I191" s="7" t="n"/>
+      <c r="G191" s="16" t="n"/>
+      <c r="H191" s="16" t="n"/>
+      <c r="I191" s="16" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="7" t="n"/>
       <c r="B192" s="7" t="n"/>
       <c r="C192" s="7" t="n"/>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D192" s="16" t="inlineStr">
         <is>
           <t>nova_table_id</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E192" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F192" s="16" t="inlineStr">
         <is>
           <t>purchase表格中的id</t>
         </is>
       </c>
-      <c r="G192" s="7" t="n"/>
-      <c r="H192" s="7" t="n"/>
-      <c r="I192" s="7" t="n"/>
+      <c r="G192" s="16" t="n"/>
+      <c r="H192" s="16" t="n"/>
+      <c r="I192" s="16" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="7" t="n"/>
       <c r="B193" s="7" t="n"/>
       <c r="C193" s="7" t="n"/>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="D193" s="16" t="inlineStr">
         <is>
           <t>nova_price</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E193" s="16" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F193" s="16" t="inlineStr">
         <is>
           <t>purchase表格中price字段的值</t>
         </is>
       </c>
-      <c r="G193" s="7" t="n"/>
-      <c r="H193" s="7" t="n"/>
-      <c r="I193" s="7" t="n"/>
+      <c r="G193" s="16" t="n"/>
+      <c r="H193" s="16" t="n"/>
+      <c r="I193" s="16" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="7" t="n"/>
       <c r="B194" s="7" t="n"/>
       <c r="C194" s="7" t="n"/>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="D194" s="16" t="inlineStr">
         <is>
           <t>nova_channel</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E194" s="16" t="inlineStr">
         <is>
           <t>enum-string</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F194" s="16" t="inlineStr">
         <is>
           <t>ios 商店</t>
         </is>
       </c>
-      <c r="G194" s="7" t="n"/>
-      <c r="H194" s="7" t="n"/>
-      <c r="I194" s="7" t="n"/>
-    </row>
-    <row r="195" ht="29" customHeight="1" s="5">
+      <c r="G194" s="16" t="n"/>
+      <c r="H194" s="16" t="n"/>
+      <c r="I194" s="16" t="n"/>
+    </row>
+    <row r="195">
       <c r="A195" s="7" t="n"/>
       <c r="B195" s="7" t="n"/>
       <c r="C195" s="7" t="n"/>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="D195" s="16" t="inlineStr">
         <is>
           <t>nova_order_id</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="E195" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F195" s="16" t="inlineStr">
         <is>
           <t>订单id</t>
         </is>
       </c>
-      <c r="G195" s="7" t="n"/>
-      <c r="H195" s="7" t="n"/>
-      <c r="I195" s="7" t="n"/>
-    </row>
-    <row r="196" ht="29" customHeight="1" s="5">
+      <c r="G195" s="16" t="n"/>
+      <c r="H195" s="16" t="n"/>
+      <c r="I195" s="16" t="n"/>
+    </row>
+    <row r="196">
       <c r="A196" s="7" t="n"/>
       <c r="B196" s="7" t="n"/>
       <c r="C196" s="7" t="n"/>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="D196" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_type_id</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E196" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F196" s="16" t="inlineStr">
         <is>
           <t>第三方支付渠道ID
 (仅第三方支付时有值)</t>
         </is>
       </c>
-      <c r="G196" s="7" t="n"/>
-      <c r="H196" s="7" t="n"/>
-      <c r="I196" s="7" t="n"/>
-    </row>
-    <row r="197" ht="14.5" customHeight="1" s="5">
+      <c r="G196" s="16" t="n"/>
+      <c r="H196" s="16" t="n"/>
+      <c r="I196" s="16" t="n"/>
+    </row>
+    <row r="197">
       <c r="A197" s="7" t="n"/>
       <c r="B197" s="7" t="n"/>
       <c r="C197" s="7" t="n"/>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="D197" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_method</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="E197" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F197" s="16" t="inlineStr">
         <is>
           <t>第三方支付渠道名字
 (仅第三方支付时有值)</t>
         </is>
       </c>
-      <c r="G197" s="7" t="n"/>
-      <c r="H197" s="7" t="n"/>
-      <c r="I197" s="7" t="n"/>
-    </row>
-    <row r="198" ht="14.5" customHeight="1" s="5">
+      <c r="G197" s="16" t="n"/>
+      <c r="H197" s="16" t="n"/>
+      <c r="I197" s="16" t="n"/>
+    </row>
+    <row r="198">
       <c r="A198" s="7" t="n"/>
       <c r="B198" s="7" t="n"/>
       <c r="C198" s="7" t="n"/>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="D198" s="16" t="inlineStr">
         <is>
           <t>nova_product_id</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F198" s="2" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="G198" s="7" t="n"/>
-      <c r="H198" s="7" t="n"/>
-      <c r="I198" s="7" t="n"/>
-    </row>
-    <row r="199" ht="14.5" customHeight="1" s="5">
+      <c r="E198" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F198" s="16" t="inlineStr">
+        <is>
+          <t>平台商品 ID / SKU（既有服务端约定，需由服务端核验实际值）。</t>
+        </is>
+      </c>
+      <c r="G198" s="16" t="n"/>
+      <c r="H198" s="16" t="n"/>
+      <c r="I198" s="16" t="n"/>
+    </row>
+    <row r="199">
       <c r="A199" s="8" t="n"/>
       <c r="B199" s="8" t="n"/>
       <c r="C199" s="8" t="n"/>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="D199" s="16" t="inlineStr">
         <is>
           <t>nova_uid</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E199" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F199" s="16" t="inlineStr">
         <is>
           <t>游戏用户唯一标识</t>
         </is>
       </c>
-      <c r="G199" s="8" t="n"/>
-      <c r="H199" s="8" t="n"/>
-      <c r="I199" s="8" t="n"/>
-    </row>
-    <row r="200" ht="14.5" customHeight="1" s="5">
-      <c r="A200" s="4" t="inlineStr">
+      <c r="G199" s="16" t="n"/>
+      <c r="H199" s="16" t="n"/>
+      <c r="I199" s="16" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="14" t="inlineStr">
         <is>
           <t>nova_iap_third_pay_order_removed</t>
         </is>
       </c>
-      <c r="B200" s="4" t="inlineStr">
+      <c r="B200" s="14" t="inlineStr">
         <is>
           <t>ThirdPay 本地订单删除</t>
         </is>
       </c>
-      <c r="C200" s="4" t="inlineStr">
+      <c r="C200" s="15" t="inlineStr">
         <is>
           <t>ThirdPay 本地订单实际移除后的可观测事件。</t>
         </is>
       </c>
-      <c r="D200" s="3" t="inlineStr">
+      <c r="D200" s="16" t="inlineStr">
         <is>
           <t>nova_table_id</t>
         </is>
       </c>
-      <c r="E200" s="3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F200" s="3" t="inlineStr">
-        <is>
-          <t>商品配置表行 ID。</t>
-        </is>
-      </c>
-      <c r="G200" s="4" t="inlineStr">
+      <c r="E200" s="16" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F200" s="16" t="inlineStr">
+        <is>
+          <t>商品配置表行 ID；客户端使用 64 位整数。</t>
+        </is>
+      </c>
+      <c r="G200" s="16" t="inlineStr">
         <is>
           <t>仅在 RemoveOrder 返回 true 后上报。</t>
         </is>
       </c>
-      <c r="H200" s="4" t="inlineStr">
+      <c r="H200" s="16" t="inlineStr">
         <is>
           <t>tga</t>
         </is>
       </c>
-      <c r="I200" s="4" t="inlineStr">
+      <c r="I200" s="16" t="inlineStr">
         <is>
           <t>删除原因使用 nova_order_delete_reason；不写 nova_reason，避免与支付失败原因混用。</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="14.5" customHeight="1" s="5">
+    <row r="201">
       <c r="A201" s="7" t="n"/>
       <c r="B201" s="7" t="n"/>
       <c r="C201" s="7" t="n"/>
-      <c r="D201" s="3" t="inlineStr">
+      <c r="D201" s="16" t="inlineStr">
         <is>
           <t>nova_product_id</t>
         </is>
       </c>
-      <c r="E201" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F201" s="3" t="inlineStr">
+      <c r="E201" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F201" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 商品 ID。</t>
         </is>
       </c>
-      <c r="G201" s="7" t="n"/>
-      <c r="H201" s="7" t="n"/>
-      <c r="I201" s="7" t="n"/>
-    </row>
-    <row r="202" ht="14.5" customHeight="1" s="5">
+      <c r="G201" s="16" t="n"/>
+      <c r="H201" s="16" t="n"/>
+      <c r="I201" s="16" t="n"/>
+    </row>
+    <row r="202">
       <c r="A202" s="7" t="n"/>
       <c r="B202" s="7" t="n"/>
       <c r="C202" s="7" t="n"/>
-      <c r="D202" s="3" t="inlineStr">
+      <c r="D202" s="16" t="inlineStr">
         <is>
           <t>nova_debug</t>
         </is>
       </c>
-      <c r="E202" s="3" t="inlineStr">
+      <c r="E202" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F202" s="3" t="inlineStr">
-        <is>
-          <t>是否测试模式。</t>
-        </is>
-      </c>
-      <c r="G202" s="7" t="n"/>
-      <c r="H202" s="7" t="n"/>
-      <c r="I202" s="7" t="n"/>
-    </row>
-    <row r="203" ht="14.5" customHeight="1" s="5">
+      <c r="F202" s="16" t="inlineStr">
+        <is>
+          <t>是否 DevelopMode.Debug；不是 AlwaysPaySucceed。</t>
+        </is>
+      </c>
+      <c r="G202" s="16" t="n"/>
+      <c r="H202" s="16" t="n"/>
+      <c r="I202" s="16" t="n"/>
+    </row>
+    <row r="203">
       <c r="A203" s="7" t="n"/>
       <c r="B203" s="7" t="n"/>
       <c r="C203" s="7" t="n"/>
-      <c r="D203" s="3" t="inlineStr">
+      <c r="D203" s="16" t="inlineStr">
         <is>
           <t>nova_price</t>
         </is>
       </c>
-      <c r="E203" s="3" t="inlineStr">
+      <c r="E203" s="16" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F203" s="3" t="inlineStr">
-        <is>
-          <t>商品本地化价格数值。</t>
-        </is>
-      </c>
-      <c r="G203" s="7" t="n"/>
-      <c r="H203" s="7" t="n"/>
-      <c r="I203" s="7" t="n"/>
-    </row>
-    <row r="204" ht="14.5" customHeight="1" s="5">
+      <c r="F203" s="16" t="inlineStr">
+        <is>
+          <t>支付表 Price 配置解析的价格数值；不是平台本地化价格或可信实付金额。</t>
+        </is>
+      </c>
+      <c r="G203" s="16" t="n"/>
+      <c r="H203" s="16" t="n"/>
+      <c r="I203" s="16" t="n"/>
+    </row>
+    <row r="204">
       <c r="A204" s="7" t="n"/>
       <c r="B204" s="7" t="n"/>
       <c r="C204" s="7" t="n"/>
-      <c r="D204" s="3" t="inlineStr">
+      <c r="D204" s="16" t="inlineStr">
         <is>
           <t>nova_channel</t>
         </is>
       </c>
-      <c r="E204" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F204" s="3" t="inlineStr">
-        <is>
-          <t>支付渠道名称。</t>
-        </is>
-      </c>
-      <c r="G204" s="7" t="n"/>
-      <c r="H204" s="7" t="n"/>
-      <c r="I204" s="7" t="n"/>
-    </row>
-    <row r="205" ht="14.5" customHeight="1" s="5">
+      <c r="E204" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F204" s="16" t="inlineStr">
+        <is>
+          <t>固定为 thirdpay。</t>
+        </is>
+      </c>
+      <c r="G204" s="16" t="n"/>
+      <c r="H204" s="16" t="n"/>
+      <c r="I204" s="16" t="n"/>
+    </row>
+    <row r="205">
       <c r="A205" s="7" t="n"/>
       <c r="B205" s="7" t="n"/>
       <c r="C205" s="7" t="n"/>
-      <c r="D205" s="3" t="inlineStr">
+      <c r="D205" s="16" t="inlineStr">
         <is>
           <t>nova_add_order</t>
         </is>
       </c>
-      <c r="E205" s="3" t="inlineStr">
+      <c r="E205" s="16" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F205" s="3" t="inlineStr">
+      <c r="F205" s="16" t="inlineStr">
         <is>
           <t>是否为补单订单。</t>
         </is>
       </c>
-      <c r="G205" s="7" t="n"/>
-      <c r="H205" s="7" t="n"/>
-      <c r="I205" s="7" t="n"/>
-    </row>
-    <row r="206" ht="14.5" customHeight="1" s="5">
+      <c r="G205" s="16" t="n"/>
+      <c r="H205" s="16" t="n"/>
+      <c r="I205" s="16" t="n"/>
+    </row>
+    <row r="206">
       <c r="A206" s="7" t="n"/>
       <c r="B206" s="7" t="n"/>
       <c r="C206" s="7" t="n"/>
-      <c r="D206" s="3" t="inlineStr">
+      <c r="D206" s="16" t="inlineStr">
         <is>
           <t>nova_validate_count</t>
         </is>
       </c>
-      <c r="E206" s="3" t="inlineStr">
+      <c r="E206" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F206" s="3" t="inlineStr">
+      <c r="F206" s="16" t="inlineStr">
         <is>
           <t>删除前已执行的验单次数；支付页未建立会话时为 0。</t>
         </is>
       </c>
-      <c r="G206" s="7" t="n"/>
-      <c r="H206" s="7" t="n"/>
-      <c r="I206" s="7" t="n"/>
-    </row>
-    <row r="207" ht="14.5" customHeight="1" s="5">
+      <c r="G206" s="16" t="n"/>
+      <c r="H206" s="16" t="n"/>
+      <c r="I206" s="16" t="n"/>
+    </row>
+    <row r="207">
       <c r="A207" s="7" t="n"/>
       <c r="B207" s="7" t="n"/>
       <c r="C207" s="7" t="n"/>
-      <c r="D207" s="3" t="inlineStr">
+      <c r="D207" s="16" t="inlineStr">
         <is>
           <t>nova_custom_data</t>
         </is>
       </c>
-      <c r="E207" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F207" s="3" t="inlineStr">
-        <is>
-          <t>业务层透传的自定义字符串参数。</t>
-        </is>
-      </c>
-      <c r="G207" s="7" t="n"/>
-      <c r="H207" s="7" t="n"/>
-      <c r="I207" s="7" t="n"/>
-    </row>
-    <row r="208" ht="14.5" customHeight="1" s="5">
+      <c r="E207" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F207" s="16" t="inlineStr">
+        <is>
+          <t>仅业务透传字符串非空时附带；框架不解析。</t>
+        </is>
+      </c>
+      <c r="G207" s="16" t="n"/>
+      <c r="H207" s="16" t="n"/>
+      <c r="I207" s="16" t="n"/>
+    </row>
+    <row r="208">
       <c r="A208" s="7" t="n"/>
       <c r="B208" s="7" t="n"/>
       <c r="C208" s="7" t="n"/>
-      <c r="D208" s="3" t="inlineStr">
+      <c r="D208" s="16" t="inlineStr">
         <is>
           <t>nova_order_delete_reason</t>
         </is>
       </c>
-      <c r="E208" s="3" t="inlineStr">
+      <c r="E208" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F208" s="3" t="inlineStr">
+      <c r="F208" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 本地订单删除原因：0=未知，1=已支付，2=已发货，3=待支付达到上限，4=失败或过期，5=不存在，6=支付页未打开，7=授权失败，8=URL 构建失败，9=用户或账号变化，10=显式清理，11=本地订单非法。</t>
         </is>
       </c>
-      <c r="G208" s="7" t="n"/>
-      <c r="H208" s="7" t="n"/>
-      <c r="I208" s="7" t="n"/>
-    </row>
-    <row r="209" ht="14.5" customHeight="1" s="5">
+      <c r="G208" s="16" t="n"/>
+      <c r="H208" s="16" t="n"/>
+      <c r="I208" s="16" t="n"/>
+    </row>
+    <row r="209">
       <c r="A209" s="7" t="n"/>
       <c r="B209" s="7" t="n"/>
       <c r="C209" s="7" t="n"/>
-      <c r="D209" s="3" t="inlineStr">
+      <c r="D209" s="16" t="inlineStr">
         <is>
           <t>nova_reason_detail</t>
         </is>
       </c>
-      <c r="E209" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F209" s="3" t="inlineStr">
+      <c r="E209" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F209" s="16" t="inlineStr">
         <is>
           <t>删除原因中文描述，与 nova_order_delete_reason 的枚举值一一对应。</t>
         </is>
       </c>
-      <c r="G209" s="7" t="n"/>
-      <c r="H209" s="7" t="n"/>
-      <c r="I209" s="7" t="n"/>
-    </row>
-    <row r="210" ht="14.5" customHeight="1" s="5">
+      <c r="G209" s="16" t="n"/>
+      <c r="H209" s="16" t="n"/>
+      <c r="I209" s="16" t="n"/>
+    </row>
+    <row r="210">
       <c r="A210" s="7" t="n"/>
       <c r="B210" s="7" t="n"/>
       <c r="C210" s="7" t="n"/>
-      <c r="D210" s="3" t="inlineStr">
+      <c r="D210" s="16" t="inlineStr">
         <is>
           <t>nova_validation_scene</t>
         </is>
       </c>
-      <c r="E210" s="3" t="inlineStr">
+      <c r="E210" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F210" s="3" t="inlineStr">
+      <c r="F210" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 验单场景：0=未知，1=应用内成功 callback，2=应用内支付页模糊返回，3=新支付前预检，4=启动或后台补单，5=外部浏览器返回兜底，6=外部浏览器成功 callback。</t>
         </is>
       </c>
-      <c r="G210" s="7" t="n"/>
-      <c r="H210" s="7" t="n"/>
-      <c r="I210" s="7" t="n"/>
-    </row>
-    <row r="211" ht="14.5" customHeight="1" s="5">
+      <c r="G210" s="16" t="n"/>
+      <c r="H210" s="16" t="n"/>
+      <c r="I210" s="16" t="n"/>
+    </row>
+    <row r="211">
       <c r="A211" s="7" t="n"/>
       <c r="B211" s="7" t="n"/>
       <c r="C211" s="7" t="n"/>
-      <c r="D211" s="3" t="inlineStr">
+      <c r="D211" s="16" t="inlineStr">
         <is>
           <t>nova_server_order_status</t>
         </is>
       </c>
-      <c r="E211" s="3" t="inlineStr">
+      <c r="E211" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F211" s="3" t="inlineStr">
+      <c r="F211" s="16" t="inlineStr">
         <is>
           <t>服务端 PbNetThirdVerifyOrderStatus：0=未指定或无有效响应，1=待支付，2=支付中，3=已支付，4=失败或过期，5=已发货，6=订单不存在。</t>
         </is>
       </c>
-      <c r="G211" s="7" t="n"/>
-      <c r="H211" s="7" t="n"/>
-      <c r="I211" s="7" t="n"/>
-    </row>
-    <row r="212" ht="14.5" customHeight="1" s="5">
+      <c r="G211" s="16" t="n"/>
+      <c r="H211" s="16" t="n"/>
+      <c r="I211" s="16" t="n"/>
+    </row>
+    <row r="212">
       <c r="A212" s="7" t="n"/>
       <c r="B212" s="7" t="n"/>
       <c r="C212" s="7" t="n"/>
-      <c r="D212" s="3" t="inlineStr">
+      <c r="D212" s="16" t="inlineStr">
         <is>
           <t>nova_client_order_status</t>
         </is>
       </c>
-      <c r="E212" s="3" t="inlineStr">
+      <c r="E212" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F212" s="3" t="inlineStr">
+      <c r="F212" s="16" t="inlineStr">
         <is>
           <t>客户端归一化订单状态：0=未知，1=已支付可发货，2=已发货，3=待支付，4=处理中，5=失败或过期，6=不存在，7=响应缺单，8=网络失败，9=验单服务不可用，10=未知服务端状态。</t>
         </is>
       </c>
-      <c r="G212" s="7" t="n"/>
-      <c r="H212" s="7" t="n"/>
-      <c r="I212" s="7" t="n"/>
-    </row>
-    <row r="213" ht="29" customHeight="1" s="5">
+      <c r="G212" s="16" t="n"/>
+      <c r="H212" s="16" t="n"/>
+      <c r="I212" s="16" t="n"/>
+    </row>
+    <row r="213">
       <c r="A213" s="7" t="n"/>
       <c r="B213" s="7" t="n"/>
       <c r="C213" s="7" t="n"/>
-      <c r="D213" s="3" t="inlineStr">
+      <c r="D213" s="16" t="inlineStr">
         <is>
           <t>nova_third_pay_failure_reason</t>
         </is>
       </c>
-      <c r="E213" s="3" t="inlineStr">
+      <c r="E213" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F213" s="3" t="inlineStr">
+      <c r="F213" s="16" t="inlineStr">
         <is>
           <t>ThirdPay 支付/验单失败原因：0=未知，1=Store 禁用，2=Store 未初始化，3=重复支付，4=商品不存在，5=UID 缺失，6=支付配置不可用，7=服务端关闭支付，8=服务端未配置商品，9=WebView 服务不可用，10=外部浏览器服务不可用，11=Google 连接失败，12=Google token 创建失败，13=Google 支付 URL 构建失败，14=Google 用户取消，15=支付页打开失败，16=支付页打开异常，17=系统浏览器回退 URL 为空，18=callback 支付失败，19=callback 参数无效，20=callback 状态未知，21=callback 订单不匹配，22=callback 到达时已开始验单，23=外部浏览器返回无成功 callback，24=验单服务不可用，25=验单网络失败，26=验单响应缺少订单，27=服务端待支付，28=服务端处理中，29=服务端失败或过期，30=服务端订单不存在，31=未知服务端订单状态，32=操作取消，33=会话被替换，34=Store 释放，35=未分类异常，36=第三方支付 URL 构建失败，37=授权完成但支付 URL 缺失。</t>
         </is>
       </c>
-      <c r="G213" s="7" t="n"/>
-      <c r="H213" s="7" t="n"/>
-      <c r="I213" s="7" t="n"/>
+      <c r="G213" s="16" t="n"/>
+      <c r="H213" s="16" t="n"/>
+      <c r="I213" s="16" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="7" t="n"/>
       <c r="B214" s="7" t="n"/>
       <c r="C214" s="7" t="n"/>
-      <c r="D214" s="3" t="inlineStr">
+      <c r="D214" s="16" t="inlineStr">
         <is>
           <t>nova_protocol_code</t>
         </is>
       </c>
-      <c r="E214" s="3" t="inlineStr">
+      <c r="E214" s="16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F214" s="3" t="inlineStr">
+      <c r="F214" s="16" t="inlineStr">
         <is>
           <t>本次删除关联的网络/协议错误码；无协议错误或未发起服务端请求时为 0。</t>
         </is>
       </c>
-      <c r="G214" s="7" t="n"/>
-      <c r="H214" s="7" t="n"/>
-      <c r="I214" s="7" t="n"/>
+      <c r="G214" s="16" t="n"/>
+      <c r="H214" s="16" t="n"/>
+      <c r="I214" s="16" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="7" t="n"/>
       <c r="B215" s="7" t="n"/>
       <c r="C215" s="7" t="n"/>
-      <c r="D215" s="3" t="inlineStr">
+      <c r="D215" s="16" t="inlineStr">
         <is>
           <t>nova_protocol_message</t>
         </is>
       </c>
-      <c r="E215" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F215" s="3" t="inlineStr">
+      <c r="E215" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F215" s="16" t="inlineStr">
         <is>
           <t>本次删除关联的网络/协议错误描述；无错误时为空。</t>
         </is>
       </c>
-      <c r="G215" s="7" t="n"/>
-      <c r="H215" s="7" t="n"/>
-      <c r="I215" s="7" t="n"/>
+      <c r="G215" s="16" t="n"/>
+      <c r="H215" s="16" t="n"/>
+      <c r="I215" s="16" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="7" t="n"/>
       <c r="B216" s="7" t="n"/>
       <c r="C216" s="7" t="n"/>
-      <c r="D216" s="3" t="inlineStr">
+      <c r="D216" s="16" t="inlineStr">
         <is>
           <t>nova_client_order_id</t>
         </is>
       </c>
-      <c r="E216" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F216" s="3" t="inlineStr">
+      <c r="E216" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F216" s="16" t="inlineStr">
         <is>
           <t>客户端生成的 ThirdPay 订单号。</t>
         </is>
       </c>
-      <c r="G216" s="7" t="n"/>
-      <c r="H216" s="7" t="n"/>
-      <c r="I216" s="7" t="n"/>
+      <c r="G216" s="16" t="n"/>
+      <c r="H216" s="16" t="n"/>
+      <c r="I216" s="16" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="8" t="n"/>
       <c r="B217" s="8" t="n"/>
       <c r="C217" s="8" t="n"/>
-      <c r="D217" s="3" t="inlineStr">
+      <c r="D217" s="16" t="inlineStr">
         <is>
           <t>nova_server_order_id</t>
         </is>
       </c>
-      <c r="E217" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F217" s="3" t="inlineStr">
+      <c r="E217" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F217" s="16" t="inlineStr">
         <is>
           <t>服务端确认的 ThirdPay 订单号；无返回时为空。</t>
         </is>
       </c>
-      <c r="G217" s="8" t="n"/>
-      <c r="H217" s="8" t="n"/>
-      <c r="I217" s="8" t="n"/>
+      <c r="G217" s="16" t="n"/>
+      <c r="H217" s="16" t="n"/>
+      <c r="I217" s="16" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="96">
+  <autoFilter ref="A1:I217"/>
+  <mergeCells count="48">
     <mergeCell ref="C138:C153"/>
-    <mergeCell ref="H83:H99"/>
-    <mergeCell ref="H130:H137"/>
-    <mergeCell ref="G112:G115"/>
-    <mergeCell ref="I112:I115"/>
-    <mergeCell ref="G27:G42"/>
     <mergeCell ref="B166:B182"/>
-    <mergeCell ref="I27:I42"/>
     <mergeCell ref="A43:A62"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="I100:I111"/>
-    <mergeCell ref="G11:G26"/>
-    <mergeCell ref="H200:H217"/>
-    <mergeCell ref="I11:I26"/>
     <mergeCell ref="A11:A26"/>
-    <mergeCell ref="G116:G129"/>
-    <mergeCell ref="I116:I129"/>
     <mergeCell ref="C100:C111"/>
-    <mergeCell ref="G83:G99"/>
-    <mergeCell ref="I83:I99"/>
     <mergeCell ref="C63:C82"/>
-    <mergeCell ref="G183:G199"/>
-    <mergeCell ref="H138:H153"/>
+    <mergeCell ref="A166:A182"/>
     <mergeCell ref="A130:A137"/>
-    <mergeCell ref="A166:A182"/>
     <mergeCell ref="C43:C62"/>
     <mergeCell ref="C166:C182"/>
-    <mergeCell ref="I183:I199"/>
     <mergeCell ref="C5:C10"/>
-    <mergeCell ref="G130:G137"/>
-    <mergeCell ref="G166:G182"/>
-    <mergeCell ref="G200:G217"/>
     <mergeCell ref="B100:B111"/>
     <mergeCell ref="A200:A217"/>
     <mergeCell ref="C112:C115"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="I154:I165"/>
     <mergeCell ref="C116:C129"/>
     <mergeCell ref="A138:A153"/>
-    <mergeCell ref="H183:H199"/>
     <mergeCell ref="B83:B99"/>
     <mergeCell ref="B183:B199"/>
     <mergeCell ref="A83:A99"/>
     <mergeCell ref="C27:C42"/>
-    <mergeCell ref="H5:H10"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="C11:C26"/>
-    <mergeCell ref="I43:I62"/>
-    <mergeCell ref="H112:H115"/>
+    <mergeCell ref="B154:B165"/>
     <mergeCell ref="C83:C99"/>
-    <mergeCell ref="B154:B165"/>
-    <mergeCell ref="H27:H42"/>
     <mergeCell ref="A183:A199"/>
+    <mergeCell ref="C183:C199"/>
     <mergeCell ref="B138:B153"/>
-    <mergeCell ref="H116:H129"/>
-    <mergeCell ref="C183:C199"/>
     <mergeCell ref="A63:A82"/>
     <mergeCell ref="C154:C165"/>
-    <mergeCell ref="I130:I137"/>
     <mergeCell ref="B63:B82"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B11:B26"/>
     <mergeCell ref="A5:A10"/>
     <mergeCell ref="C130:C137"/>
     <mergeCell ref="B43:B62"/>
-    <mergeCell ref="H63:H82"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="H11:H26"/>
-    <mergeCell ref="I200:I217"/>
     <mergeCell ref="B5:B10"/>
     <mergeCell ref="A27:A42"/>
-    <mergeCell ref="G154:G165"/>
-    <mergeCell ref="H166:H182"/>
     <mergeCell ref="A100:A111"/>
     <mergeCell ref="A116:A129"/>
-    <mergeCell ref="G138:G153"/>
-    <mergeCell ref="I138:I153"/>
-    <mergeCell ref="H154:H165"/>
-    <mergeCell ref="G100:G111"/>
     <mergeCell ref="B130:B137"/>
-    <mergeCell ref="G63:G82"/>
-    <mergeCell ref="I63:I82"/>
     <mergeCell ref="B112:B115"/>
-    <mergeCell ref="G43:G62"/>
     <mergeCell ref="B200:B217"/>
     <mergeCell ref="B27:B42"/>
-    <mergeCell ref="G5:G10"/>
     <mergeCell ref="A112:A115"/>
-    <mergeCell ref="I5:I10"/>
-    <mergeCell ref="I166:I182"/>
-    <mergeCell ref="H43:H62"/>
     <mergeCell ref="C200:C217"/>
-    <mergeCell ref="H100:H111"/>
     <mergeCell ref="B116:B129"/>
     <mergeCell ref="A154:A165"/>
   </mergeCells>
